--- a/results_ollamaSharp_laptop.xlsx
+++ b/results_ollamaSharp_laptop.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\susan\Documents\bachelor-thesis_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5992A3-7B97-4DE7-93ED-EC07407E0AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3236A64-F886-4882-8888-894B0E61FEDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="7845" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="36">
   <si>
     <t>FilePath</t>
   </si>
@@ -123,6 +136,12 @@
   <si>
     <t>laptop\02_ollamaSharp\testresults_en_h_3.md</t>
   </si>
+  <si>
+    <t>ms/token</t>
+  </si>
+  <si>
+    <t>% of stream + gen</t>
+  </si>
 </sst>
 </file>
 
@@ -156,8 +175,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -460,32 +480,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T96"/>
+  <dimension ref="A1:W96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
     <col min="2" max="2" width="2.42578125" customWidth="1"/>
     <col min="3" max="3" width="6.140625" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="4" max="5" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" customWidth="1"/>
-    <col min="9" max="9" width="9.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" customWidth="1"/>
-    <col min="11" max="11" width="9.140625" customWidth="1"/>
-    <col min="12" max="12" width="7.28515625" customWidth="1"/>
-    <col min="13" max="13" width="7.5703125" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" customWidth="1"/>
-    <col min="19" max="19" width="11.42578125" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" customWidth="1"/>
+    <col min="7" max="7" width="8" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.85546875" customWidth="1"/>
+    <col min="11" max="11" width="5.5703125" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" customWidth="1"/>
+    <col min="15" max="15" width="7.28515625" customWidth="1"/>
+    <col min="16" max="16" width="7.5703125" customWidth="1"/>
+    <col min="17" max="17" width="6.7109375" customWidth="1"/>
+    <col min="18" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="13.28515625" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" customWidth="1"/>
+    <col min="21" max="21" width="11.140625" customWidth="1"/>
+    <col min="22" max="22" width="11.42578125" customWidth="1"/>
+    <col min="23" max="23" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -495,59 +516,68 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="U1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="V1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -557,59 +587,71 @@
       <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
+        <f>(H2+J2)*1000/F2</f>
+        <v>1093.522727272727</v>
+      </c>
+      <c r="E2" s="1">
+        <f>J2*1000/F2</f>
+        <v>597.38636363636363</v>
+      </c>
+      <c r="F2">
         <v>88</v>
       </c>
-      <c r="E2">
+      <c r="G2" s="1">
         <v>8.75</v>
       </c>
-      <c r="F2">
+      <c r="H2" s="1">
         <v>43.66</v>
       </c>
-      <c r="G2">
+      <c r="I2" s="1">
+        <f>(H2+J2)/100*H2</f>
+        <v>42.014017999999993</v>
+      </c>
+      <c r="J2">
         <v>52.57</v>
       </c>
-      <c r="H2">
+      <c r="K2">
         <v>61.32</v>
       </c>
-      <c r="I2">
+      <c r="L2">
         <v>730</v>
       </c>
-      <c r="J2">
+      <c r="M2">
         <v>4440</v>
       </c>
-      <c r="K2">
+      <c r="N2">
         <v>3689</v>
       </c>
-      <c r="L2">
+      <c r="O2">
         <v>39</v>
       </c>
-      <c r="M2">
+      <c r="P2">
         <v>57</v>
       </c>
-      <c r="N2">
+      <c r="Q2">
         <v>52</v>
       </c>
-      <c r="O2">
+      <c r="R2">
         <v>631</v>
       </c>
-      <c r="P2">
+      <c r="S2">
         <v>787</v>
       </c>
-      <c r="Q2">
+      <c r="T2">
         <v>780</v>
       </c>
-      <c r="R2">
+      <c r="U2">
         <v>60</v>
       </c>
-      <c r="S2">
+      <c r="V2">
         <v>3596</v>
       </c>
-      <c r="T2">
+      <c r="W2">
         <v>2857</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -619,59 +661,71 @@
       <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
+        <f t="shared" ref="D3:D66" si="0">(H3+J3)*1000/F3</f>
+        <v>682.32558139534888</v>
+      </c>
+      <c r="E3" s="1">
+        <f t="shared" ref="E3:E66" si="1">J3*1000/F3</f>
+        <v>392.40310077519382</v>
+      </c>
+      <c r="F3">
         <v>129</v>
       </c>
-      <c r="E3">
+      <c r="G3" s="1">
         <v>2.41</v>
       </c>
-      <c r="F3">
+      <c r="H3" s="1">
         <v>37.4</v>
       </c>
-      <c r="G3">
+      <c r="I3" s="1">
+        <f t="shared" ref="I3:I66" si="2">(H3+J3)/100*H3</f>
+        <v>32.91948</v>
+      </c>
+      <c r="J3">
         <v>50.62</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>53.03</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>4439</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>4443</v>
       </c>
-      <c r="K3">
+      <c r="N3">
         <v>4441</v>
       </c>
-      <c r="L3">
+      <c r="O3">
         <v>56</v>
       </c>
-      <c r="M3">
+      <c r="P3">
         <v>57</v>
       </c>
-      <c r="N3">
+      <c r="Q3">
         <v>56</v>
       </c>
-      <c r="O3">
+      <c r="R3">
         <v>788</v>
       </c>
-      <c r="P3">
+      <c r="S3">
         <v>788</v>
       </c>
-      <c r="Q3">
+      <c r="T3">
         <v>788</v>
       </c>
-      <c r="R3">
+      <c r="U3">
         <v>3594</v>
       </c>
-      <c r="S3">
+      <c r="V3">
         <v>3598</v>
       </c>
-      <c r="T3">
+      <c r="W3">
         <v>3597</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -681,59 +735,71 @@
       <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>875.85106382978734</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>488.82978723404256</v>
+      </c>
+      <c r="F4">
         <v>94</v>
       </c>
-      <c r="E4">
+      <c r="G4" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F4">
+      <c r="H4" s="1">
         <v>36.380000000000003</v>
       </c>
-      <c r="G4">
+      <c r="I4" s="1">
+        <f t="shared" si="2"/>
+        <v>29.951654000000008</v>
+      </c>
+      <c r="J4">
         <v>45.95</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <v>48.43</v>
       </c>
-      <c r="I4">
+      <c r="L4">
         <v>4446</v>
       </c>
-      <c r="J4">
+      <c r="M4">
         <v>4449</v>
       </c>
-      <c r="K4">
+      <c r="N4">
         <v>4447</v>
       </c>
-      <c r="L4">
+      <c r="O4">
         <v>57</v>
       </c>
-      <c r="M4">
+      <c r="P4">
         <v>58</v>
       </c>
-      <c r="N4">
+      <c r="Q4">
         <v>57</v>
       </c>
-      <c r="O4">
+      <c r="R4">
         <v>790</v>
       </c>
-      <c r="P4">
+      <c r="S4">
         <v>790</v>
       </c>
-      <c r="Q4">
+      <c r="T4">
         <v>790</v>
       </c>
-      <c r="R4">
+      <c r="U4">
         <v>3599</v>
       </c>
-      <c r="S4">
+      <c r="V4">
         <v>3601</v>
       </c>
-      <c r="T4">
+      <c r="W4">
         <v>3600</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -743,59 +809,71 @@
       <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
+        <f t="shared" si="0"/>
+        <v>497.75147928994085</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="1"/>
+        <v>299.46745562130178</v>
+      </c>
+      <c r="F5">
         <v>169</v>
       </c>
-      <c r="E5">
+      <c r="G5" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F5">
+      <c r="H5" s="1">
         <v>33.51</v>
       </c>
-      <c r="G5">
+      <c r="I5" s="1">
+        <f t="shared" si="2"/>
+        <v>28.188611999999999</v>
+      </c>
+      <c r="J5">
         <v>50.61</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <v>53.06</v>
       </c>
-      <c r="I5">
+      <c r="L5">
         <v>4451</v>
       </c>
-      <c r="J5">
+      <c r="M5">
         <v>4454</v>
       </c>
-      <c r="K5">
+      <c r="N5">
         <v>4452</v>
       </c>
-      <c r="L5">
+      <c r="O5">
         <v>57</v>
       </c>
-      <c r="M5">
+      <c r="P5">
         <v>58</v>
       </c>
-      <c r="N5">
+      <c r="Q5">
         <v>57</v>
       </c>
-      <c r="O5">
+      <c r="R5">
         <v>792</v>
       </c>
-      <c r="P5">
+      <c r="S5">
         <v>792</v>
       </c>
-      <c r="Q5">
+      <c r="T5">
         <v>792</v>
       </c>
-      <c r="R5">
+      <c r="U5">
         <v>3601</v>
       </c>
-      <c r="S5">
+      <c r="V5">
         <v>3604</v>
       </c>
-      <c r="T5">
+      <c r="W5">
         <v>3602</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -805,59 +883,71 @@
       <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>1189.0909090909092</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>645.63636363636363</v>
+      </c>
+      <c r="F6">
         <v>55</v>
       </c>
-      <c r="E6">
+      <c r="G6" s="1">
         <v>2.36</v>
       </c>
-      <c r="F6">
+      <c r="H6" s="1">
         <v>29.89</v>
       </c>
-      <c r="G6">
+      <c r="I6" s="1">
+        <f t="shared" si="2"/>
+        <v>19.54806</v>
+      </c>
+      <c r="J6">
         <v>35.51</v>
       </c>
-      <c r="H6">
+      <c r="K6">
         <v>37.869999999999997</v>
       </c>
-      <c r="I6">
+      <c r="L6">
         <v>4457</v>
       </c>
-      <c r="J6">
+      <c r="M6">
         <v>4462</v>
       </c>
-      <c r="K6">
+      <c r="N6">
         <v>4458</v>
       </c>
-      <c r="L6">
+      <c r="O6">
         <v>58</v>
       </c>
-      <c r="M6">
+      <c r="P6">
         <v>59</v>
       </c>
-      <c r="N6">
+      <c r="Q6">
         <v>58</v>
       </c>
-      <c r="O6">
+      <c r="R6">
         <v>795</v>
       </c>
-      <c r="P6">
+      <c r="S6">
         <v>795</v>
       </c>
-      <c r="Q6">
+      <c r="T6">
         <v>795</v>
       </c>
-      <c r="R6">
+      <c r="U6">
         <v>3604</v>
       </c>
-      <c r="S6">
+      <c r="V6">
         <v>3607</v>
       </c>
-      <c r="T6">
+      <c r="W6">
         <v>3605</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>20</v>
       </c>
@@ -867,59 +957,71 @@
       <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="1">
+        <f t="shared" si="0"/>
+        <v>571.63742690058484</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="1"/>
+        <v>336.84210526315792</v>
+      </c>
+      <c r="F7">
         <v>171</v>
       </c>
-      <c r="E7">
+      <c r="G7" s="1">
         <v>2.41</v>
       </c>
-      <c r="F7">
+      <c r="H7" s="1">
         <v>40.15</v>
       </c>
-      <c r="G7">
+      <c r="I7" s="1">
+        <f t="shared" si="2"/>
+        <v>39.246625000000002</v>
+      </c>
+      <c r="J7">
         <v>57.6</v>
       </c>
-      <c r="H7">
+      <c r="K7">
         <v>60.01</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>4462</v>
       </c>
-      <c r="J7">
+      <c r="M7">
         <v>4472</v>
       </c>
-      <c r="K7">
+      <c r="N7">
         <v>4464</v>
       </c>
-      <c r="L7">
+      <c r="O7">
         <v>58</v>
       </c>
-      <c r="M7">
+      <c r="P7">
         <v>62</v>
       </c>
-      <c r="N7">
+      <c r="Q7">
         <v>59</v>
       </c>
-      <c r="O7">
+      <c r="R7">
         <v>797</v>
       </c>
-      <c r="P7">
+      <c r="S7">
         <v>797</v>
       </c>
-      <c r="Q7">
+      <c r="T7">
         <v>797</v>
       </c>
-      <c r="R7">
+      <c r="U7">
         <v>3606</v>
       </c>
-      <c r="S7">
+      <c r="V7">
         <v>3613</v>
       </c>
-      <c r="T7">
+      <c r="W7">
         <v>3608</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -929,59 +1031,71 @@
       <c r="C8" t="s">
         <v>21</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>328.04154302670622</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>215.7566765578635</v>
+      </c>
+      <c r="F8">
         <v>337</v>
       </c>
-      <c r="E8">
+      <c r="G8" s="1">
         <v>2.42</v>
       </c>
-      <c r="F8">
+      <c r="H8" s="1">
         <v>37.840000000000003</v>
       </c>
-      <c r="G8">
+      <c r="I8" s="1">
+        <f t="shared" si="2"/>
+        <v>41.832120000000003</v>
+      </c>
+      <c r="J8">
         <v>72.709999999999994</v>
       </c>
-      <c r="H8">
+      <c r="K8">
         <v>75.13</v>
       </c>
-      <c r="I8">
+      <c r="L8">
         <v>4468</v>
       </c>
-      <c r="J8">
+      <c r="M8">
         <v>4471</v>
       </c>
-      <c r="K8">
+      <c r="N8">
         <v>4470</v>
       </c>
-      <c r="L8">
+      <c r="O8">
         <v>58</v>
       </c>
-      <c r="M8">
+      <c r="P8">
         <v>59</v>
       </c>
-      <c r="N8">
+      <c r="Q8">
         <v>59</v>
       </c>
-      <c r="O8">
+      <c r="R8">
         <v>800</v>
       </c>
-      <c r="P8">
+      <c r="S8">
         <v>800</v>
       </c>
-      <c r="Q8">
+      <c r="T8">
         <v>800</v>
       </c>
-      <c r="R8">
+      <c r="U8">
         <v>3610</v>
       </c>
-      <c r="S8">
+      <c r="V8">
         <v>3613</v>
       </c>
-      <c r="T8">
+      <c r="W8">
         <v>3611</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -991,59 +1105,71 @@
       <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
+        <f t="shared" si="0"/>
+        <v>997.67123287671234</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="1"/>
+        <v>539.58904109589037</v>
+      </c>
+      <c r="F9">
         <v>73</v>
       </c>
-      <c r="E9">
+      <c r="G9" s="1">
         <v>7.15</v>
       </c>
-      <c r="F9">
+      <c r="H9" s="1">
         <v>33.44</v>
       </c>
-      <c r="G9">
+      <c r="I9" s="1">
+        <f t="shared" si="2"/>
+        <v>24.354351999999995</v>
+      </c>
+      <c r="J9">
         <v>39.39</v>
       </c>
-      <c r="H9">
+      <c r="K9">
         <v>46.54</v>
       </c>
-      <c r="I9">
+      <c r="L9">
         <v>733</v>
       </c>
-      <c r="J9">
+      <c r="M9">
         <v>4317</v>
       </c>
-      <c r="K9">
+      <c r="N9">
         <v>3567</v>
       </c>
-      <c r="L9">
+      <c r="O9">
         <v>39</v>
       </c>
-      <c r="M9">
+      <c r="P9">
         <v>58</v>
       </c>
-      <c r="N9">
+      <c r="Q9">
         <v>52</v>
       </c>
-      <c r="O9">
+      <c r="R9">
         <v>635</v>
       </c>
-      <c r="P9">
+      <c r="S9">
         <v>787</v>
       </c>
-      <c r="Q9">
+      <c r="T9">
         <v>779</v>
       </c>
-      <c r="R9">
+      <c r="U9">
         <v>59</v>
       </c>
-      <c r="S9">
+      <c r="V9">
         <v>3473</v>
       </c>
-      <c r="T9">
+      <c r="W9">
         <v>2735</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -1053,59 +1179,71 @@
       <c r="C10" t="s">
         <v>21</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>781.16279069767438</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>435.11627906976742</v>
+      </c>
+      <c r="F10">
         <v>86</v>
       </c>
-      <c r="E10">
+      <c r="G10" s="1">
         <v>2.46</v>
       </c>
-      <c r="F10">
+      <c r="H10" s="1">
         <v>29.76</v>
       </c>
-      <c r="G10">
+      <c r="I10" s="1">
+        <f t="shared" si="2"/>
+        <v>19.992768000000002</v>
+      </c>
+      <c r="J10">
         <v>37.42</v>
       </c>
-      <c r="H10">
+      <c r="K10">
         <v>39.880000000000003</v>
       </c>
-      <c r="I10">
+      <c r="L10">
         <v>4316</v>
       </c>
-      <c r="J10">
+      <c r="M10">
         <v>4324</v>
       </c>
-      <c r="K10">
+      <c r="N10">
         <v>4322</v>
       </c>
-      <c r="L10">
+      <c r="O10">
         <v>57</v>
       </c>
-      <c r="M10">
+      <c r="P10">
         <v>58</v>
       </c>
-      <c r="N10">
+      <c r="Q10">
         <v>57</v>
       </c>
-      <c r="O10">
+      <c r="R10">
         <v>788</v>
       </c>
-      <c r="P10">
+      <c r="S10">
         <v>789</v>
       </c>
-      <c r="Q10">
+      <c r="T10">
         <v>789</v>
       </c>
-      <c r="R10">
+      <c r="U10">
         <v>3470</v>
       </c>
-      <c r="S10">
+      <c r="V10">
         <v>3478</v>
       </c>
-      <c r="T10">
+      <c r="W10">
         <v>3476</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1115,59 +1253,71 @@
       <c r="C11" t="s">
         <v>21</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
+        <f t="shared" si="0"/>
+        <v>513.24503311258275</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="1"/>
+        <v>304.37086092715231</v>
+      </c>
+      <c r="F11">
         <v>151</v>
       </c>
-      <c r="E11">
+      <c r="G11" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F11">
+      <c r="H11" s="1">
         <v>31.54</v>
       </c>
-      <c r="G11">
+      <c r="I11" s="1">
+        <f t="shared" si="2"/>
+        <v>24.4435</v>
+      </c>
+      <c r="J11">
         <v>45.96</v>
       </c>
-      <c r="H11">
+      <c r="K11">
         <v>48.43</v>
       </c>
-      <c r="I11">
+      <c r="L11">
         <v>4326</v>
       </c>
-      <c r="J11">
+      <c r="M11">
         <v>4330</v>
       </c>
-      <c r="K11">
+      <c r="N11">
         <v>4327</v>
       </c>
-      <c r="L11">
+      <c r="O11">
         <v>57</v>
       </c>
-      <c r="M11">
+      <c r="P11">
         <v>59</v>
       </c>
-      <c r="N11">
+      <c r="Q11">
         <v>58</v>
       </c>
-      <c r="O11">
+      <c r="R11">
         <v>790</v>
       </c>
-      <c r="P11">
+      <c r="S11">
         <v>791</v>
       </c>
-      <c r="Q11">
+      <c r="T11">
         <v>790</v>
       </c>
-      <c r="R11">
+      <c r="U11">
         <v>3478</v>
       </c>
-      <c r="S11">
+      <c r="V11">
         <v>3481</v>
       </c>
-      <c r="T11">
+      <c r="W11">
         <v>3479</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1177,59 +1327,71 @@
       <c r="C12" t="s">
         <v>21</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>519.38775510204084</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>309.52380952380952</v>
+      </c>
+      <c r="F12">
         <v>147</v>
       </c>
-      <c r="E12">
+      <c r="G12" s="1">
         <v>2.5</v>
       </c>
-      <c r="F12">
+      <c r="H12" s="1">
         <v>30.85</v>
       </c>
-      <c r="G12">
+      <c r="I12" s="1">
+        <f t="shared" si="2"/>
+        <v>23.553975000000001</v>
+      </c>
+      <c r="J12">
         <v>45.5</v>
       </c>
-      <c r="H12">
+      <c r="K12">
         <v>48</v>
       </c>
-      <c r="I12">
+      <c r="L12">
         <v>4331</v>
       </c>
-      <c r="J12">
+      <c r="M12">
         <v>4335</v>
       </c>
-      <c r="K12">
+      <c r="N12">
         <v>4334</v>
       </c>
-      <c r="L12">
+      <c r="O12">
         <v>58</v>
       </c>
-      <c r="M12">
+      <c r="P12">
         <v>59</v>
       </c>
-      <c r="N12">
+      <c r="Q12">
         <v>58</v>
       </c>
-      <c r="O12">
+      <c r="R12">
         <v>793</v>
       </c>
-      <c r="P12">
+      <c r="S12">
         <v>794</v>
       </c>
-      <c r="Q12">
+      <c r="T12">
         <v>794</v>
       </c>
-      <c r="R12">
+      <c r="U12">
         <v>3481</v>
       </c>
-      <c r="S12">
+      <c r="V12">
         <v>3483</v>
       </c>
-      <c r="T12">
+      <c r="W12">
         <v>3482</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1239,59 +1401,71 @@
       <c r="C13" t="s">
         <v>21</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="1">
+        <f t="shared" si="0"/>
+        <v>2342.2222222222222</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="1"/>
+        <v>1220.7407407407406</v>
+      </c>
+      <c r="F13">
         <v>27</v>
       </c>
-      <c r="E13">
+      <c r="G13" s="1">
         <v>2.4900000000000002</v>
       </c>
-      <c r="F13">
+      <c r="H13" s="1">
         <v>30.28</v>
       </c>
-      <c r="G13">
+      <c r="I13" s="1">
+        <f t="shared" si="2"/>
+        <v>19.149072000000004</v>
+      </c>
+      <c r="J13">
         <v>32.96</v>
       </c>
-      <c r="H13">
+      <c r="K13">
         <v>35.44</v>
       </c>
-      <c r="I13">
+      <c r="L13">
         <v>4337</v>
       </c>
-      <c r="J13">
+      <c r="M13">
         <v>4347</v>
       </c>
-      <c r="K13">
+      <c r="N13">
         <v>4341</v>
       </c>
-      <c r="L13">
+      <c r="O13">
         <v>58</v>
       </c>
-      <c r="M13">
+      <c r="P13">
         <v>62</v>
       </c>
-      <c r="N13">
+      <c r="Q13">
         <v>60</v>
       </c>
-      <c r="O13">
+      <c r="R13">
         <v>795</v>
       </c>
-      <c r="P13">
+      <c r="S13">
         <v>795</v>
       </c>
-      <c r="Q13">
+      <c r="T13">
         <v>795</v>
       </c>
-      <c r="R13">
+      <c r="U13">
         <v>3484</v>
       </c>
-      <c r="S13">
+      <c r="V13">
         <v>3489</v>
       </c>
-      <c r="T13">
+      <c r="W13">
         <v>3486</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1301,59 +1475,71 @@
       <c r="C14" t="s">
         <v>21</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
+        <f t="shared" si="0"/>
+        <v>905.357142857143</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="1"/>
+        <v>504.04761904761904</v>
+      </c>
+      <c r="F14">
         <v>84</v>
       </c>
-      <c r="E14">
+      <c r="G14" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F14">
+      <c r="H14" s="1">
         <v>33.71</v>
       </c>
-      <c r="G14">
+      <c r="I14" s="1">
+        <f t="shared" si="2"/>
+        <v>25.636455000000002</v>
+      </c>
+      <c r="J14">
         <v>42.34</v>
       </c>
-      <c r="H14">
+      <c r="K14">
         <v>44.81</v>
       </c>
-      <c r="I14">
+      <c r="L14">
         <v>4347</v>
       </c>
-      <c r="J14">
+      <c r="M14">
         <v>4351</v>
       </c>
-      <c r="K14">
+      <c r="N14">
         <v>4349</v>
       </c>
-      <c r="L14">
+      <c r="O14">
         <v>61</v>
       </c>
-      <c r="M14">
+      <c r="P14">
         <v>63</v>
       </c>
-      <c r="N14">
+      <c r="Q14">
         <v>61</v>
       </c>
-      <c r="O14">
+      <c r="R14">
         <v>797</v>
       </c>
-      <c r="P14">
+      <c r="S14">
         <v>798</v>
       </c>
-      <c r="Q14">
+      <c r="T14">
         <v>798</v>
       </c>
-      <c r="R14">
+      <c r="U14">
         <v>3489</v>
       </c>
-      <c r="S14">
+      <c r="V14">
         <v>3491</v>
       </c>
-      <c r="T14">
+      <c r="W14">
         <v>3490</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1363,59 +1549,71 @@
       <c r="C15" t="s">
         <v>21</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
+        <f t="shared" si="0"/>
+        <v>339.90853658536588</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="1"/>
+        <v>220.97560975609755</v>
+      </c>
+      <c r="F15">
         <v>328</v>
       </c>
-      <c r="E15">
+      <c r="G15" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F15">
+      <c r="H15" s="1">
         <v>39.01</v>
       </c>
-      <c r="G15">
+      <c r="I15" s="1">
+        <f t="shared" si="2"/>
+        <v>43.492249000000001</v>
+      </c>
+      <c r="J15">
         <v>72.48</v>
       </c>
-      <c r="H15">
+      <c r="K15">
         <v>74.930000000000007</v>
       </c>
-      <c r="I15">
+      <c r="L15">
         <v>4354</v>
       </c>
-      <c r="J15">
+      <c r="M15">
         <v>4362</v>
       </c>
-      <c r="K15">
+      <c r="N15">
         <v>4356</v>
       </c>
-      <c r="L15">
+      <c r="O15">
         <v>61</v>
       </c>
-      <c r="M15">
+      <c r="P15">
         <v>65</v>
       </c>
-      <c r="N15">
+      <c r="Q15">
         <v>62</v>
       </c>
-      <c r="O15">
+      <c r="R15">
         <v>801</v>
       </c>
-      <c r="P15">
+      <c r="S15">
         <v>801</v>
       </c>
-      <c r="Q15">
+      <c r="T15">
         <v>801</v>
       </c>
-      <c r="R15">
+      <c r="U15">
         <v>3492</v>
       </c>
-      <c r="S15">
+      <c r="V15">
         <v>3496</v>
       </c>
-      <c r="T15">
+      <c r="W15">
         <v>3493</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -1425,59 +1623,71 @@
       <c r="C16" t="s">
         <v>21</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
+        <f t="shared" si="0"/>
+        <v>704.8</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="1"/>
+        <v>402.72</v>
+      </c>
+      <c r="F16">
         <v>125</v>
       </c>
-      <c r="E16">
+      <c r="G16" s="1">
         <v>2.48</v>
       </c>
-      <c r="F16">
+      <c r="H16" s="1">
         <v>37.76</v>
       </c>
-      <c r="G16">
+      <c r="I16" s="1">
+        <f t="shared" si="2"/>
+        <v>33.266559999999991</v>
+      </c>
+      <c r="J16">
         <v>50.34</v>
       </c>
-      <c r="H16">
+      <c r="K16">
         <v>52.82</v>
       </c>
-      <c r="I16">
+      <c r="L16">
         <v>4357</v>
       </c>
-      <c r="J16">
+      <c r="M16">
         <v>4369</v>
       </c>
-      <c r="K16">
+      <c r="N16">
         <v>4360</v>
       </c>
-      <c r="L16">
+      <c r="O16">
         <v>61</v>
       </c>
-      <c r="M16">
+      <c r="P16">
         <v>67</v>
       </c>
-      <c r="N16">
+      <c r="Q16">
         <v>62</v>
       </c>
-      <c r="O16">
+      <c r="R16">
         <v>802</v>
       </c>
-      <c r="P16">
+      <c r="S16">
         <v>803</v>
       </c>
-      <c r="Q16">
+      <c r="T16">
         <v>803</v>
       </c>
-      <c r="R16">
+      <c r="U16">
         <v>3488</v>
       </c>
-      <c r="S16">
+      <c r="V16">
         <v>3500</v>
       </c>
-      <c r="T16">
+      <c r="W16">
         <v>3495</v>
       </c>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -1487,59 +1697,71 @@
       <c r="C17" t="s">
         <v>21</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="1">
+        <f t="shared" si="0"/>
+        <v>1163.3766233766235</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="1"/>
+        <v>631.55844155844159</v>
+      </c>
+      <c r="F17">
         <v>77</v>
       </c>
-      <c r="E17">
+      <c r="G17" s="1">
         <v>6.9</v>
       </c>
-      <c r="F17">
+      <c r="H17" s="1">
         <v>40.950000000000003</v>
       </c>
-      <c r="G17">
+      <c r="I17" s="1">
+        <f t="shared" si="2"/>
+        <v>36.68301000000001</v>
+      </c>
+      <c r="J17">
         <v>48.63</v>
       </c>
-      <c r="H17">
+      <c r="K17">
         <v>55.54</v>
       </c>
-      <c r="I17">
+      <c r="L17">
         <v>734</v>
       </c>
-      <c r="J17">
+      <c r="M17">
         <v>4424</v>
       </c>
-      <c r="K17">
+      <c r="N17">
         <v>3768</v>
       </c>
-      <c r="L17">
+      <c r="O17">
         <v>39</v>
       </c>
-      <c r="M17">
+      <c r="P17">
         <v>57</v>
       </c>
-      <c r="N17">
+      <c r="Q17">
         <v>51</v>
       </c>
-      <c r="O17">
+      <c r="R17">
         <v>635</v>
       </c>
-      <c r="P17">
+      <c r="S17">
         <v>786</v>
       </c>
-      <c r="Q17">
+      <c r="T17">
         <v>780</v>
       </c>
-      <c r="R17">
+      <c r="U17">
         <v>60</v>
       </c>
-      <c r="S17">
+      <c r="V17">
         <v>3581</v>
       </c>
-      <c r="T17">
+      <c r="W17">
         <v>2936</v>
       </c>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -1549,59 +1771,71 @@
       <c r="C18" t="s">
         <v>21</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="1">
+        <f t="shared" si="0"/>
+        <v>572.625</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="1"/>
+        <v>338.1875</v>
+      </c>
+      <c r="F18">
         <v>160</v>
       </c>
-      <c r="E18">
+      <c r="G18" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F18">
+      <c r="H18" s="1">
         <v>37.51</v>
       </c>
-      <c r="G18">
+      <c r="I18" s="1">
+        <f t="shared" si="2"/>
+        <v>34.366661999999998</v>
+      </c>
+      <c r="J18">
         <v>54.11</v>
       </c>
-      <c r="H18">
+      <c r="K18">
         <v>56.57</v>
       </c>
-      <c r="I18">
+      <c r="L18">
         <v>4426</v>
       </c>
-      <c r="J18">
+      <c r="M18">
         <v>4429</v>
       </c>
-      <c r="K18">
+      <c r="N18">
         <v>4427</v>
       </c>
-      <c r="L18">
+      <c r="O18">
         <v>56</v>
       </c>
-      <c r="M18">
+      <c r="P18">
         <v>57</v>
       </c>
-      <c r="N18">
+      <c r="Q18">
         <v>56</v>
       </c>
-      <c r="O18">
+      <c r="R18">
         <v>788</v>
       </c>
-      <c r="P18">
+      <c r="S18">
         <v>788</v>
       </c>
-      <c r="Q18">
+      <c r="T18">
         <v>788</v>
       </c>
-      <c r="R18">
+      <c r="U18">
         <v>3581</v>
       </c>
-      <c r="S18">
+      <c r="V18">
         <v>3584</v>
       </c>
-      <c r="T18">
+      <c r="W18">
         <v>3582</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -1611,59 +1845,71 @@
       <c r="C19" t="s">
         <v>21</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="1">
+        <f t="shared" si="0"/>
+        <v>505.48387096774201</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="1"/>
+        <v>303.76344086021504</v>
+      </c>
+      <c r="F19">
         <v>186</v>
       </c>
-      <c r="E19">
+      <c r="G19" s="1">
         <v>2.5</v>
       </c>
-      <c r="F19">
+      <c r="H19" s="1">
         <v>37.520000000000003</v>
       </c>
-      <c r="G19">
+      <c r="I19" s="1">
+        <f t="shared" si="2"/>
+        <v>35.27630400000001</v>
+      </c>
+      <c r="J19">
         <v>56.5</v>
       </c>
-      <c r="H19">
+      <c r="K19">
         <v>59</v>
       </c>
-      <c r="I19">
+      <c r="L19">
         <v>4431</v>
       </c>
-      <c r="J19">
+      <c r="M19">
         <v>4434</v>
       </c>
-      <c r="K19">
+      <c r="N19">
         <v>4433</v>
       </c>
-      <c r="L19">
+      <c r="O19">
         <v>57</v>
       </c>
-      <c r="M19">
+      <c r="P19">
         <v>58</v>
       </c>
-      <c r="N19">
+      <c r="Q19">
         <v>57</v>
       </c>
-      <c r="O19">
+      <c r="R19">
         <v>790</v>
       </c>
-      <c r="P19">
+      <c r="S19">
         <v>790</v>
       </c>
-      <c r="Q19">
+      <c r="T19">
         <v>790</v>
       </c>
-      <c r="R19">
+      <c r="U19">
         <v>3585</v>
       </c>
-      <c r="S19">
+      <c r="V19">
         <v>3587</v>
       </c>
-      <c r="T19">
+      <c r="W19">
         <v>3586</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -1673,59 +1919,71 @@
       <c r="C20" t="s">
         <v>21</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
+        <f t="shared" si="0"/>
+        <v>699.43396226415098</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="1"/>
+        <v>399.71698113207549</v>
+      </c>
+      <c r="F20">
         <v>106</v>
       </c>
-      <c r="E20">
+      <c r="G20" s="1">
         <v>2.48</v>
       </c>
-      <c r="F20">
+      <c r="H20" s="1">
         <v>31.77</v>
       </c>
-      <c r="G20">
+      <c r="I20" s="1">
+        <f t="shared" si="2"/>
+        <v>23.554278</v>
+      </c>
+      <c r="J20">
         <v>42.37</v>
       </c>
-      <c r="H20">
+      <c r="K20">
         <v>44.85</v>
       </c>
-      <c r="I20">
+      <c r="L20">
         <v>4438</v>
       </c>
-      <c r="J20">
+      <c r="M20">
         <v>4440</v>
       </c>
-      <c r="K20">
+      <c r="N20">
         <v>4438</v>
       </c>
-      <c r="L20">
+      <c r="O20">
         <v>58</v>
       </c>
-      <c r="M20">
+      <c r="P20">
         <v>59</v>
       </c>
-      <c r="N20">
+      <c r="Q20">
         <v>58</v>
       </c>
-      <c r="O20">
+      <c r="R20">
         <v>792</v>
       </c>
-      <c r="P20">
+      <c r="S20">
         <v>793</v>
       </c>
-      <c r="Q20">
+      <c r="T20">
         <v>793</v>
       </c>
-      <c r="R20">
+      <c r="U20">
         <v>3587</v>
       </c>
-      <c r="S20">
+      <c r="V20">
         <v>3589</v>
       </c>
-      <c r="T20">
+      <c r="W20">
         <v>3588</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -1735,59 +1993,71 @@
       <c r="C21" t="s">
         <v>21</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
+        <f t="shared" si="0"/>
+        <v>2481.1999999999998</v>
+      </c>
+      <c r="E21" s="1">
+        <f t="shared" si="1"/>
+        <v>1290.3999999999999</v>
+      </c>
+      <c r="F21">
         <v>25</v>
       </c>
-      <c r="E21">
+      <c r="G21" s="1">
         <v>2.46</v>
       </c>
-      <c r="F21">
+      <c r="H21" s="1">
         <v>29.77</v>
       </c>
-      <c r="G21">
+      <c r="I21" s="1">
+        <f t="shared" si="2"/>
+        <v>18.466331</v>
+      </c>
+      <c r="J21">
         <v>32.26</v>
       </c>
-      <c r="H21">
+      <c r="K21">
         <v>34.729999999999997</v>
       </c>
-      <c r="I21">
+      <c r="L21">
         <v>4442</v>
       </c>
-      <c r="J21">
+      <c r="M21">
         <v>4454</v>
       </c>
-      <c r="K21">
+      <c r="N21">
         <v>4445</v>
       </c>
-      <c r="L21">
+      <c r="O21">
         <v>58</v>
       </c>
-      <c r="M21">
+      <c r="P21">
         <v>63</v>
       </c>
-      <c r="N21">
+      <c r="Q21">
         <v>59</v>
       </c>
-      <c r="O21">
+      <c r="R21">
         <v>794</v>
       </c>
-      <c r="P21">
+      <c r="S21">
         <v>795</v>
       </c>
-      <c r="Q21">
+      <c r="T21">
         <v>795</v>
       </c>
-      <c r="R21">
+      <c r="U21">
         <v>3589</v>
       </c>
-      <c r="S21">
+      <c r="V21">
         <v>3596</v>
       </c>
-      <c r="T21">
+      <c r="W21">
         <v>3591</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -1797,59 +2067,71 @@
       <c r="C22" t="s">
         <v>21</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="1">
+        <f t="shared" si="0"/>
+        <v>1139.4202898550725</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" si="1"/>
+        <v>621.304347826087</v>
+      </c>
+      <c r="F22">
         <v>69</v>
       </c>
-      <c r="E22">
+      <c r="G22" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F22">
+      <c r="H22" s="1">
         <v>35.75</v>
       </c>
-      <c r="G22">
+      <c r="I22" s="1">
+        <f t="shared" si="2"/>
+        <v>28.106650000000002</v>
+      </c>
+      <c r="J22">
         <v>42.87</v>
       </c>
-      <c r="H22">
+      <c r="K22">
         <v>45.32</v>
       </c>
-      <c r="I22">
+      <c r="L22">
         <v>4455</v>
       </c>
-      <c r="J22">
+      <c r="M22">
         <v>4460</v>
       </c>
-      <c r="K22">
+      <c r="N22">
         <v>4457</v>
       </c>
-      <c r="L22">
+      <c r="O22">
         <v>62</v>
       </c>
-      <c r="M22">
+      <c r="P22">
         <v>64</v>
       </c>
-      <c r="N22">
+      <c r="Q22">
         <v>63</v>
       </c>
-      <c r="O22">
+      <c r="R22">
         <v>797</v>
       </c>
-      <c r="P22">
+      <c r="S22">
         <v>797</v>
       </c>
-      <c r="Q22">
+      <c r="T22">
         <v>797</v>
       </c>
-      <c r="R22">
+      <c r="U22">
         <v>3596</v>
       </c>
-      <c r="S22">
+      <c r="V22">
         <v>3599</v>
       </c>
-      <c r="T22">
+      <c r="W22">
         <v>3597</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -1859,59 +2141,71 @@
       <c r="C23" t="s">
         <v>21</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="1">
+        <f t="shared" si="0"/>
+        <v>377.36334405144697</v>
+      </c>
+      <c r="E23" s="1">
+        <f t="shared" si="1"/>
+        <v>240.2572347266881</v>
+      </c>
+      <c r="F23">
         <v>311</v>
       </c>
-      <c r="E23">
+      <c r="G23" s="1">
         <v>2.44</v>
       </c>
-      <c r="F23">
+      <c r="H23" s="1">
         <v>42.64</v>
       </c>
-      <c r="G23">
+      <c r="I23" s="1">
+        <f t="shared" si="2"/>
+        <v>50.042304000000001</v>
+      </c>
+      <c r="J23">
         <v>74.72</v>
       </c>
-      <c r="H23">
+      <c r="K23">
         <v>77.16</v>
       </c>
-      <c r="I23">
+      <c r="L23">
         <v>4461</v>
       </c>
-      <c r="J23">
+      <c r="M23">
         <v>4470</v>
       </c>
-      <c r="K23">
+      <c r="N23">
         <v>4463</v>
       </c>
-      <c r="L23">
+      <c r="O23">
         <v>63</v>
       </c>
-      <c r="M23">
+      <c r="P23">
         <v>67</v>
       </c>
-      <c r="N23">
+      <c r="Q23">
         <v>63</v>
       </c>
-      <c r="O23">
+      <c r="R23">
         <v>800</v>
       </c>
-      <c r="P23">
+      <c r="S23">
         <v>800</v>
       </c>
-      <c r="Q23">
+      <c r="T23">
         <v>800</v>
       </c>
-      <c r="R23">
+      <c r="U23">
         <v>3599</v>
       </c>
-      <c r="S23">
+      <c r="V23">
         <v>3603</v>
       </c>
-      <c r="T23">
+      <c r="W23">
         <v>3600</v>
       </c>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -1921,59 +2215,71 @@
       <c r="C24" t="s">
         <v>21</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="1">
+        <f t="shared" si="0"/>
+        <v>639.17808219178085</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="1"/>
+        <v>370.34246575342468</v>
+      </c>
+      <c r="F24">
         <v>146</v>
       </c>
-      <c r="E24">
+      <c r="G24" s="1">
         <v>2.37</v>
       </c>
-      <c r="F24">
+      <c r="H24" s="1">
         <v>39.25</v>
       </c>
-      <c r="G24">
+      <c r="I24" s="1">
+        <f t="shared" si="2"/>
+        <v>36.628099999999996</v>
+      </c>
+      <c r="J24">
         <v>54.07</v>
       </c>
-      <c r="H24">
+      <c r="K24">
         <v>56.44</v>
       </c>
-      <c r="I24">
+      <c r="L24">
         <v>4466</v>
       </c>
-      <c r="J24">
+      <c r="M24">
         <v>4477</v>
       </c>
-      <c r="K24">
+      <c r="N24">
         <v>4468</v>
       </c>
-      <c r="L24">
+      <c r="O24">
         <v>63</v>
       </c>
-      <c r="M24">
+      <c r="P24">
         <v>68</v>
       </c>
-      <c r="N24">
+      <c r="Q24">
         <v>64</v>
       </c>
-      <c r="O24">
+      <c r="R24">
         <v>801</v>
       </c>
-      <c r="P24">
+      <c r="S24">
         <v>802</v>
       </c>
-      <c r="Q24">
+      <c r="T24">
         <v>802</v>
       </c>
-      <c r="R24">
+      <c r="U24">
         <v>3601</v>
       </c>
-      <c r="S24">
+      <c r="V24">
         <v>3607</v>
       </c>
-      <c r="T24">
+      <c r="W24">
         <v>3603</v>
       </c>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1983,59 +2289,71 @@
       <c r="C25" t="s">
         <v>21</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="1">
+        <f t="shared" si="0"/>
+        <v>365.93155893536129</v>
+      </c>
+      <c r="E25" s="1">
+        <f t="shared" si="1"/>
+        <v>206.76806083650189</v>
+      </c>
+      <c r="F25">
         <v>263</v>
       </c>
-      <c r="E25">
+      <c r="G25" s="1">
         <v>7.01</v>
       </c>
-      <c r="F25">
+      <c r="H25" s="1">
         <v>41.86</v>
       </c>
-      <c r="G25">
+      <c r="I25" s="1">
+        <f t="shared" si="2"/>
+        <v>40.286064000000003</v>
+      </c>
+      <c r="J25">
         <v>54.38</v>
       </c>
-      <c r="H25">
+      <c r="K25">
         <v>61.38</v>
       </c>
-      <c r="I25">
+      <c r="L25">
         <v>733</v>
       </c>
-      <c r="J25">
+      <c r="M25">
         <v>4535</v>
       </c>
-      <c r="K25">
+      <c r="N25">
         <v>3894</v>
       </c>
-      <c r="L25">
+      <c r="O25">
         <v>39</v>
       </c>
-      <c r="M25">
+      <c r="P25">
         <v>58</v>
       </c>
-      <c r="N25">
+      <c r="Q25">
         <v>52</v>
       </c>
-      <c r="O25">
+      <c r="R25">
         <v>634</v>
       </c>
-      <c r="P25">
+      <c r="S25">
         <v>787</v>
       </c>
-      <c r="Q25">
+      <c r="T25">
         <v>782</v>
       </c>
-      <c r="R25">
+      <c r="U25">
         <v>60</v>
       </c>
-      <c r="S25">
+      <c r="V25">
         <v>3690</v>
       </c>
-      <c r="T25">
+      <c r="W25">
         <v>3060</v>
       </c>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -2045,59 +2363,71 @@
       <c r="C26" t="s">
         <v>21</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="1">
+        <f t="shared" si="0"/>
+        <v>965.53191489361689</v>
+      </c>
+      <c r="E26" s="1">
+        <f t="shared" si="1"/>
+        <v>535.74468085106378</v>
+      </c>
+      <c r="F26">
         <v>94</v>
       </c>
-      <c r="E26">
+      <c r="G26" s="1">
         <v>2.4900000000000002</v>
       </c>
-      <c r="F26">
+      <c r="H26" s="1">
         <v>40.4</v>
       </c>
-      <c r="G26">
+      <c r="I26" s="1">
+        <f t="shared" si="2"/>
+        <v>36.66704</v>
+      </c>
+      <c r="J26">
         <v>50.36</v>
       </c>
-      <c r="H26">
+      <c r="K26">
         <v>52.85</v>
       </c>
-      <c r="I26">
+      <c r="L26">
         <v>4534</v>
       </c>
-      <c r="J26">
+      <c r="M26">
         <v>4537</v>
       </c>
-      <c r="K26">
+      <c r="N26">
         <v>4535</v>
       </c>
-      <c r="L26">
+      <c r="O26">
         <v>57</v>
       </c>
-      <c r="M26">
+      <c r="P26">
         <v>58</v>
       </c>
-      <c r="N26">
+      <c r="Q26">
         <v>57</v>
       </c>
-      <c r="O26">
+      <c r="R26">
         <v>788</v>
       </c>
-      <c r="P26">
+      <c r="S26">
         <v>788</v>
       </c>
-      <c r="Q26">
+      <c r="T26">
         <v>788</v>
       </c>
-      <c r="R26">
+      <c r="U26">
         <v>3688</v>
       </c>
-      <c r="S26">
+      <c r="V26">
         <v>3691</v>
       </c>
-      <c r="T26">
+      <c r="W26">
         <v>3690</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -2107,59 +2437,71 @@
       <c r="C27" t="s">
         <v>21</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="1">
+        <f t="shared" si="0"/>
+        <v>1020.5882352941177</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="1"/>
+        <v>562.47058823529414</v>
+      </c>
+      <c r="F27">
         <v>85</v>
       </c>
-      <c r="E27">
+      <c r="G27" s="1">
         <v>2.5499999999999998</v>
       </c>
-      <c r="F27">
+      <c r="H27" s="1">
         <v>38.94</v>
       </c>
-      <c r="G27">
+      <c r="I27" s="1">
+        <f t="shared" si="2"/>
+        <v>33.780450000000002</v>
+      </c>
+      <c r="J27">
         <v>47.81</v>
       </c>
-      <c r="H27">
+      <c r="K27">
         <v>50.37</v>
       </c>
-      <c r="I27">
+      <c r="L27">
         <v>4540</v>
       </c>
-      <c r="J27">
+      <c r="M27">
         <v>4552</v>
       </c>
-      <c r="K27">
+      <c r="N27">
         <v>4546</v>
       </c>
-      <c r="L27">
+      <c r="O27">
         <v>57</v>
       </c>
-      <c r="M27">
+      <c r="P27">
         <v>62</v>
       </c>
-      <c r="N27">
+      <c r="Q27">
         <v>60</v>
       </c>
-      <c r="O27">
+      <c r="R27">
         <v>791</v>
       </c>
-      <c r="P27">
+      <c r="S27">
         <v>791</v>
       </c>
-      <c r="Q27">
+      <c r="T27">
         <v>791</v>
       </c>
-      <c r="R27">
+      <c r="U27">
         <v>3692</v>
       </c>
-      <c r="S27">
+      <c r="V27">
         <v>3699</v>
       </c>
-      <c r="T27">
+      <c r="W27">
         <v>3695</v>
       </c>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
@@ -2169,59 +2511,71 @@
       <c r="C28" t="s">
         <v>21</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="1">
+        <f t="shared" si="0"/>
+        <v>331.85303514376994</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="1"/>
+        <v>218.2108626198083</v>
+      </c>
+      <c r="F28">
         <v>313</v>
       </c>
-      <c r="E28">
+      <c r="G28" s="1">
         <v>2.4</v>
       </c>
-      <c r="F28">
+      <c r="H28" s="1">
         <v>35.57</v>
       </c>
-      <c r="G28">
+      <c r="I28" s="1">
+        <f t="shared" si="2"/>
+        <v>36.946559000000001</v>
+      </c>
+      <c r="J28">
         <v>68.3</v>
       </c>
-      <c r="H28">
+      <c r="K28">
         <v>70.709999999999994</v>
       </c>
-      <c r="I28">
+      <c r="L28">
         <v>4553</v>
       </c>
-      <c r="J28">
+      <c r="M28">
         <v>4558</v>
       </c>
-      <c r="K28">
+      <c r="N28">
         <v>4555</v>
       </c>
-      <c r="L28">
+      <c r="O28">
         <v>62</v>
       </c>
-      <c r="M28">
+      <c r="P28">
         <v>63</v>
       </c>
-      <c r="N28">
+      <c r="Q28">
         <v>62</v>
       </c>
-      <c r="O28">
+      <c r="R28">
         <v>793</v>
       </c>
-      <c r="P28">
+      <c r="S28">
         <v>794</v>
       </c>
-      <c r="Q28">
+      <c r="T28">
         <v>793</v>
       </c>
-      <c r="R28">
+      <c r="U28">
         <v>3698</v>
       </c>
-      <c r="S28">
+      <c r="V28">
         <v>3702</v>
       </c>
-      <c r="T28">
+      <c r="W28">
         <v>3700</v>
       </c>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -2231,59 +2585,71 @@
       <c r="C29" t="s">
         <v>21</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="1">
+        <f t="shared" si="0"/>
+        <v>2560.3571428571427</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="1"/>
+        <v>1332.1428571428571</v>
+      </c>
+      <c r="F29">
         <v>28</v>
       </c>
-      <c r="E29">
+      <c r="G29" s="1">
         <v>2.4300000000000002</v>
       </c>
-      <c r="F29">
+      <c r="H29" s="1">
         <v>34.39</v>
       </c>
-      <c r="G29">
+      <c r="I29" s="1">
+        <f t="shared" si="2"/>
+        <v>24.654191000000001</v>
+      </c>
+      <c r="J29">
         <v>37.299999999999997</v>
       </c>
-      <c r="H29">
+      <c r="K29">
         <v>39.74</v>
       </c>
-      <c r="I29">
+      <c r="L29">
         <v>4560</v>
       </c>
-      <c r="J29">
+      <c r="M29">
         <v>4565</v>
       </c>
-      <c r="K29">
+      <c r="N29">
         <v>4561</v>
       </c>
-      <c r="L29">
+      <c r="O29">
         <v>62</v>
       </c>
-      <c r="M29">
+      <c r="P29">
         <v>64</v>
       </c>
-      <c r="N29">
+      <c r="Q29">
         <v>63</v>
       </c>
-      <c r="O29">
+      <c r="R29">
         <v>795</v>
       </c>
-      <c r="P29">
+      <c r="S29">
         <v>796</v>
       </c>
-      <c r="Q29">
+      <c r="T29">
         <v>796</v>
       </c>
-      <c r="R29">
+      <c r="U29">
         <v>3702</v>
       </c>
-      <c r="S29">
+      <c r="V29">
         <v>3706</v>
       </c>
-      <c r="T29">
+      <c r="W29">
         <v>3703</v>
       </c>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>24</v>
       </c>
@@ -2293,59 +2659,71 @@
       <c r="C30" t="s">
         <v>21</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="1">
+        <f t="shared" si="0"/>
+        <v>1236.5277777777778</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="1"/>
+        <v>670.69444444444446</v>
+      </c>
+      <c r="F30">
         <v>72</v>
       </c>
-      <c r="E30">
+      <c r="G30" s="1">
         <v>2.46</v>
       </c>
-      <c r="F30">
+      <c r="H30" s="1">
         <v>40.74</v>
       </c>
-      <c r="G30">
+      <c r="I30" s="1">
+        <f t="shared" si="2"/>
+        <v>36.270822000000003</v>
+      </c>
+      <c r="J30">
         <v>48.29</v>
       </c>
-      <c r="H30">
+      <c r="K30">
         <v>50.76</v>
       </c>
-      <c r="I30">
+      <c r="L30">
         <v>4565</v>
       </c>
-      <c r="J30">
+      <c r="M30">
         <v>4568</v>
       </c>
-      <c r="K30">
+      <c r="N30">
         <v>4566</v>
       </c>
-      <c r="L30">
+      <c r="O30">
         <v>63</v>
       </c>
-      <c r="M30">
+      <c r="P30">
         <v>63</v>
       </c>
-      <c r="N30">
+      <c r="Q30">
         <v>63</v>
       </c>
-      <c r="O30">
+      <c r="R30">
         <v>798</v>
       </c>
-      <c r="P30">
+      <c r="S30">
         <v>798</v>
       </c>
-      <c r="Q30">
+      <c r="T30">
         <v>798</v>
       </c>
-      <c r="R30">
+      <c r="U30">
         <v>3705</v>
       </c>
-      <c r="S30">
+      <c r="V30">
         <v>3707</v>
       </c>
-      <c r="T30">
+      <c r="W30">
         <v>3706</v>
       </c>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>24</v>
       </c>
@@ -2355,59 +2733,71 @@
       <c r="C31" t="s">
         <v>21</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="1">
+        <f t="shared" si="0"/>
+        <v>450.9961685823755</v>
+      </c>
+      <c r="E31" s="1">
+        <f t="shared" si="1"/>
+        <v>278.58237547892719</v>
+      </c>
+      <c r="F31">
         <v>261</v>
       </c>
-      <c r="E31">
+      <c r="G31" s="1">
         <v>2.38</v>
       </c>
-      <c r="F31">
+      <c r="H31" s="1">
         <v>45</v>
       </c>
-      <c r="G31">
+      <c r="I31" s="1">
+        <f t="shared" si="2"/>
+        <v>52.969500000000004</v>
+      </c>
+      <c r="J31">
         <v>72.709999999999994</v>
       </c>
-      <c r="H31">
+      <c r="K31">
         <v>75.08</v>
       </c>
-      <c r="I31">
+      <c r="L31">
         <v>4570</v>
       </c>
-      <c r="J31">
+      <c r="M31">
         <v>4579</v>
       </c>
-      <c r="K31">
+      <c r="N31">
         <v>4572</v>
       </c>
-      <c r="L31">
+      <c r="O31">
         <v>63</v>
       </c>
-      <c r="M31">
+      <c r="P31">
         <v>67</v>
       </c>
-      <c r="N31">
+      <c r="Q31">
         <v>63</v>
       </c>
-      <c r="O31">
+      <c r="R31">
         <v>800</v>
       </c>
-      <c r="P31">
+      <c r="S31">
         <v>800</v>
       </c>
-      <c r="Q31">
+      <c r="T31">
         <v>800</v>
       </c>
-      <c r="R31">
+      <c r="U31">
         <v>3707</v>
       </c>
-      <c r="S31">
+      <c r="V31">
         <v>3711</v>
       </c>
-      <c r="T31">
+      <c r="W31">
         <v>3708</v>
       </c>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>24</v>
       </c>
@@ -2417,59 +2807,71 @@
       <c r="C32" t="s">
         <v>21</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="1">
+        <f t="shared" si="0"/>
+        <v>357.11711711711712</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="1"/>
+        <v>231.59159159159159</v>
+      </c>
+      <c r="F32">
         <v>333</v>
       </c>
-      <c r="E32">
+      <c r="G32" s="1">
         <v>2.46</v>
       </c>
-      <c r="F32">
+      <c r="H32" s="1">
         <v>41.8</v>
       </c>
-      <c r="G32">
+      <c r="I32" s="1">
+        <f t="shared" si="2"/>
+        <v>49.708559999999999</v>
+      </c>
+      <c r="J32">
         <v>77.12</v>
       </c>
-      <c r="H32">
+      <c r="K32">
         <v>79.58</v>
       </c>
-      <c r="I32">
+      <c r="L32">
         <v>4575</v>
       </c>
-      <c r="J32">
+      <c r="M32">
         <v>4586</v>
       </c>
-      <c r="K32">
+      <c r="N32">
         <v>4577</v>
       </c>
-      <c r="L32">
+      <c r="O32">
         <v>63</v>
       </c>
-      <c r="M32">
+      <c r="P32">
         <v>68</v>
       </c>
-      <c r="N32">
+      <c r="Q32">
         <v>64</v>
       </c>
-      <c r="O32">
+      <c r="R32">
         <v>803</v>
       </c>
-      <c r="P32">
+      <c r="S32">
         <v>803</v>
       </c>
-      <c r="Q32">
+      <c r="T32">
         <v>803</v>
       </c>
-      <c r="R32">
+      <c r="U32">
         <v>3709</v>
       </c>
-      <c r="S32">
+      <c r="V32">
         <v>3714</v>
       </c>
-      <c r="T32">
+      <c r="W32">
         <v>3710</v>
       </c>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>25</v>
       </c>
@@ -2479,59 +2881,71 @@
       <c r="C33" t="s">
         <v>21</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="1">
+        <f t="shared" si="0"/>
+        <v>863.47368421052636</v>
+      </c>
+      <c r="E33" s="1">
+        <f t="shared" si="1"/>
+        <v>481.15789473684208</v>
+      </c>
+      <c r="F33">
         <v>95</v>
       </c>
-      <c r="E33">
+      <c r="G33" s="1">
         <v>6.9</v>
       </c>
-      <c r="F33">
+      <c r="H33" s="1">
         <v>36.32</v>
       </c>
-      <c r="G33">
+      <c r="I33" s="1">
+        <f t="shared" si="2"/>
+        <v>29.793296000000002</v>
+      </c>
+      <c r="J33">
         <v>45.71</v>
       </c>
-      <c r="H33">
+      <c r="K33">
         <v>52.61</v>
       </c>
-      <c r="I33">
+      <c r="L33">
         <v>733</v>
       </c>
-      <c r="J33">
+      <c r="M33">
         <v>4263</v>
       </c>
-      <c r="K33">
+      <c r="N33">
         <v>3633</v>
       </c>
-      <c r="L33">
+      <c r="O33">
         <v>39</v>
       </c>
-      <c r="M33">
+      <c r="P33">
         <v>56</v>
       </c>
-      <c r="N33">
+      <c r="Q33">
         <v>52</v>
       </c>
-      <c r="O33">
+      <c r="R33">
         <v>634</v>
       </c>
-      <c r="P33">
+      <c r="S33">
         <v>786</v>
       </c>
-      <c r="Q33">
+      <c r="T33">
         <v>780</v>
       </c>
-      <c r="R33">
+      <c r="U33">
         <v>60</v>
       </c>
-      <c r="S33">
+      <c r="V33">
         <v>3421</v>
       </c>
-      <c r="T33">
+      <c r="W33">
         <v>2801</v>
       </c>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -2541,59 +2955,71 @@
       <c r="C34" t="s">
         <v>21</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="1">
+        <f t="shared" si="0"/>
+        <v>1065.2777777777776</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" si="1"/>
+        <v>581.94444444444446</v>
+      </c>
+      <c r="F34">
         <v>72</v>
       </c>
-      <c r="E34">
+      <c r="G34" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F34">
+      <c r="H34" s="1">
         <v>34.799999999999997</v>
       </c>
-      <c r="G34">
+      <c r="I34" s="1">
+        <f t="shared" si="2"/>
+        <v>26.691599999999994</v>
+      </c>
+      <c r="J34">
         <v>41.9</v>
       </c>
-      <c r="H34">
+      <c r="K34">
         <v>44.35</v>
       </c>
-      <c r="I34">
+      <c r="L34">
         <v>4263</v>
       </c>
-      <c r="J34">
+      <c r="M34">
         <v>4271</v>
       </c>
-      <c r="K34">
+      <c r="N34">
         <v>4268</v>
       </c>
-      <c r="L34">
+      <c r="O34">
         <v>56</v>
       </c>
-      <c r="M34">
+      <c r="P34">
         <v>57</v>
       </c>
-      <c r="N34">
+      <c r="Q34">
         <v>56</v>
       </c>
-      <c r="O34">
+      <c r="R34">
         <v>787</v>
       </c>
-      <c r="P34">
+      <c r="S34">
         <v>787</v>
       </c>
-      <c r="Q34">
+      <c r="T34">
         <v>787</v>
       </c>
-      <c r="R34">
+      <c r="U34">
         <v>3419</v>
       </c>
-      <c r="S34">
+      <c r="V34">
         <v>3427</v>
       </c>
-      <c r="T34">
+      <c r="W34">
         <v>3425</v>
       </c>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>25</v>
       </c>
@@ -2603,59 +3029,71 @@
       <c r="C35" t="s">
         <v>21</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="1">
+        <f t="shared" si="0"/>
+        <v>431.33004926108373</v>
+      </c>
+      <c r="E35" s="1">
+        <f t="shared" si="1"/>
+        <v>265.17241379310343</v>
+      </c>
+      <c r="F35">
         <v>203</v>
       </c>
-      <c r="E35">
+      <c r="G35" s="1">
         <v>2.4900000000000002</v>
       </c>
-      <c r="F35">
+      <c r="H35" s="1">
         <v>33.729999999999997</v>
       </c>
-      <c r="G35">
+      <c r="I35" s="1">
+        <f t="shared" si="2"/>
+        <v>29.533987999999997</v>
+      </c>
+      <c r="J35">
         <v>53.83</v>
       </c>
-      <c r="H35">
+      <c r="K35">
         <v>56.32</v>
       </c>
-      <c r="I35">
+      <c r="L35">
         <v>4273</v>
       </c>
-      <c r="J35">
+      <c r="M35">
         <v>4278</v>
       </c>
-      <c r="K35">
+      <c r="N35">
         <v>4276</v>
       </c>
-      <c r="L35">
+      <c r="O35">
         <v>57</v>
       </c>
-      <c r="M35">
+      <c r="P35">
         <v>58</v>
       </c>
-      <c r="N35">
+      <c r="Q35">
         <v>57</v>
       </c>
-      <c r="O35">
+      <c r="R35">
         <v>790</v>
       </c>
-      <c r="P35">
+      <c r="S35">
         <v>790</v>
       </c>
-      <c r="Q35">
+      <c r="T35">
         <v>790</v>
       </c>
-      <c r="R35">
+      <c r="U35">
         <v>3427</v>
       </c>
-      <c r="S35">
+      <c r="V35">
         <v>3431</v>
       </c>
-      <c r="T35">
+      <c r="W35">
         <v>3429</v>
       </c>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>25</v>
       </c>
@@ -2665,59 +3103,71 @@
       <c r="C36" t="s">
         <v>21</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="1">
+        <f t="shared" si="0"/>
+        <v>343.12741312741315</v>
+      </c>
+      <c r="E36" s="1">
+        <f t="shared" si="1"/>
+        <v>221.23552123552125</v>
+      </c>
+      <c r="F36">
         <v>259</v>
       </c>
-      <c r="E36">
+      <c r="G36" s="1">
         <v>2.46</v>
       </c>
-      <c r="F36">
+      <c r="H36" s="1">
         <v>31.57</v>
       </c>
-      <c r="G36">
+      <c r="I36" s="1">
+        <f t="shared" si="2"/>
+        <v>28.056259000000001</v>
+      </c>
+      <c r="J36">
         <v>57.3</v>
       </c>
-      <c r="H36">
+      <c r="K36">
         <v>59.77</v>
       </c>
-      <c r="I36">
+      <c r="L36">
         <v>4280</v>
       </c>
-      <c r="J36">
+      <c r="M36">
         <v>4283</v>
       </c>
-      <c r="K36">
+      <c r="N36">
         <v>4282</v>
       </c>
-      <c r="L36">
+      <c r="O36">
         <v>57</v>
       </c>
-      <c r="M36">
+      <c r="P36">
         <v>58</v>
       </c>
-      <c r="N36">
+      <c r="Q36">
         <v>57</v>
       </c>
-      <c r="O36">
+      <c r="R36">
         <v>792</v>
       </c>
-      <c r="P36">
+      <c r="S36">
         <v>792</v>
       </c>
-      <c r="Q36">
+      <c r="T36">
         <v>792</v>
       </c>
-      <c r="R36">
+      <c r="U36">
         <v>3430</v>
       </c>
-      <c r="S36">
+      <c r="V36">
         <v>3433</v>
       </c>
-      <c r="T36">
+      <c r="W36">
         <v>3432</v>
       </c>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>25</v>
       </c>
@@ -2727,59 +3177,71 @@
       <c r="C37" t="s">
         <v>21</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="1">
+        <f t="shared" si="0"/>
+        <v>602.43055555555554</v>
+      </c>
+      <c r="E37" s="1">
+        <f t="shared" si="1"/>
+        <v>350.83333333333331</v>
+      </c>
+      <c r="F37">
         <v>144</v>
       </c>
-      <c r="E37">
+      <c r="G37" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F37">
+      <c r="H37" s="1">
         <v>36.229999999999997</v>
       </c>
-      <c r="G37">
+      <c r="I37" s="1">
+        <f t="shared" si="2"/>
+        <v>31.429524999999998</v>
+      </c>
+      <c r="J37">
         <v>50.52</v>
       </c>
-      <c r="H37">
+      <c r="K37">
         <v>52.97</v>
       </c>
-      <c r="I37">
+      <c r="L37">
         <v>4286</v>
       </c>
-      <c r="J37">
+      <c r="M37">
         <v>4301</v>
       </c>
-      <c r="K37">
+      <c r="N37">
         <v>4294</v>
       </c>
-      <c r="L37">
+      <c r="O37">
         <v>58</v>
       </c>
-      <c r="M37">
+      <c r="P37">
         <v>64</v>
       </c>
-      <c r="N37">
+      <c r="Q37">
         <v>61</v>
       </c>
-      <c r="O37">
+      <c r="R37">
         <v>795</v>
       </c>
-      <c r="P37">
+      <c r="S37">
         <v>795</v>
       </c>
-      <c r="Q37">
+      <c r="T37">
         <v>795</v>
       </c>
-      <c r="R37">
+      <c r="U37">
         <v>3434</v>
       </c>
-      <c r="S37">
+      <c r="V37">
         <v>3442</v>
       </c>
-      <c r="T37">
+      <c r="W37">
         <v>3438</v>
       </c>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -2789,59 +3251,71 @@
       <c r="C38" t="s">
         <v>21</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="1">
+        <f t="shared" si="0"/>
+        <v>284.86935866983373</v>
+      </c>
+      <c r="E38" s="1">
+        <f t="shared" si="1"/>
+        <v>193.44418052256532</v>
+      </c>
+      <c r="F38">
         <v>421</v>
       </c>
-      <c r="E38">
+      <c r="G38" s="1">
         <v>2.42</v>
       </c>
-      <c r="F38">
+      <c r="H38" s="1">
         <v>38.49</v>
       </c>
-      <c r="G38">
+      <c r="I38" s="1">
+        <f t="shared" si="2"/>
+        <v>46.161057000000007</v>
+      </c>
+      <c r="J38">
         <v>81.44</v>
       </c>
-      <c r="H38">
+      <c r="K38">
         <v>83.85</v>
       </c>
-      <c r="I38">
+      <c r="L38">
         <v>4302</v>
       </c>
-      <c r="J38">
+      <c r="M38">
         <v>4308</v>
       </c>
-      <c r="K38">
+      <c r="N38">
         <v>4305</v>
       </c>
-      <c r="L38">
+      <c r="O38">
         <v>63</v>
       </c>
-      <c r="M38">
+      <c r="P38">
         <v>64</v>
       </c>
-      <c r="N38">
+      <c r="Q38">
         <v>63</v>
       </c>
-      <c r="O38">
+      <c r="R38">
         <v>797</v>
       </c>
-      <c r="P38">
+      <c r="S38">
         <v>798</v>
       </c>
-      <c r="Q38">
+      <c r="T38">
         <v>798</v>
       </c>
-      <c r="R38">
+      <c r="U38">
         <v>3441</v>
       </c>
-      <c r="S38">
+      <c r="V38">
         <v>3446</v>
       </c>
-      <c r="T38">
+      <c r="W38">
         <v>3444</v>
       </c>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>25</v>
       </c>
@@ -2851,59 +3325,71 @@
       <c r="C39" t="s">
         <v>21</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="1">
+        <f t="shared" si="0"/>
+        <v>885.3763440860215</v>
+      </c>
+      <c r="E39" s="1">
+        <f t="shared" si="1"/>
+        <v>492.15053763440858</v>
+      </c>
+      <c r="F39">
         <v>93</v>
       </c>
-      <c r="E39">
+      <c r="G39" s="1">
         <v>2.4300000000000002</v>
       </c>
-      <c r="F39">
+      <c r="H39" s="1">
         <v>36.57</v>
       </c>
-      <c r="G39">
+      <c r="I39" s="1">
+        <f t="shared" si="2"/>
+        <v>30.111738000000003</v>
+      </c>
+      <c r="J39">
         <v>45.77</v>
       </c>
-      <c r="H39">
+      <c r="K39">
         <v>48.2</v>
       </c>
-      <c r="I39">
+      <c r="L39">
         <v>4309</v>
       </c>
-      <c r="J39">
+      <c r="M39">
         <v>4317</v>
       </c>
-      <c r="K39">
+      <c r="N39">
         <v>4310</v>
       </c>
-      <c r="L39">
+      <c r="O39">
         <v>63</v>
       </c>
-      <c r="M39">
+      <c r="P39">
         <v>67</v>
       </c>
-      <c r="N39">
+      <c r="Q39">
         <v>63</v>
       </c>
-      <c r="O39">
+      <c r="R39">
         <v>800</v>
       </c>
-      <c r="P39">
+      <c r="S39">
         <v>800</v>
       </c>
-      <c r="Q39">
+      <c r="T39">
         <v>800</v>
       </c>
-      <c r="R39">
+      <c r="U39">
         <v>3446</v>
       </c>
-      <c r="S39">
+      <c r="V39">
         <v>3450</v>
       </c>
-      <c r="T39">
+      <c r="W39">
         <v>3447</v>
       </c>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>26</v>
       </c>
@@ -2913,59 +3399,71 @@
       <c r="C40" t="s">
         <v>21</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="1">
+        <f t="shared" si="0"/>
+        <v>866.48648648648646</v>
+      </c>
+      <c r="E40" s="1">
+        <f t="shared" si="1"/>
+        <v>485.13513513513516</v>
+      </c>
+      <c r="F40">
         <v>111</v>
       </c>
-      <c r="E40">
+      <c r="G40" s="1">
         <v>7.31</v>
       </c>
-      <c r="F40">
+      <c r="H40" s="1">
         <v>42.33</v>
       </c>
-      <c r="G40">
+      <c r="I40" s="1">
+        <f t="shared" si="2"/>
+        <v>40.712994000000002</v>
+      </c>
+      <c r="J40">
         <v>53.85</v>
       </c>
-      <c r="H40">
+      <c r="K40">
         <v>61.17</v>
       </c>
-      <c r="I40">
+      <c r="L40">
         <v>732</v>
       </c>
-      <c r="J40">
+      <c r="M40">
         <v>4537</v>
       </c>
-      <c r="K40">
+      <c r="N40">
         <v>3875</v>
       </c>
-      <c r="L40">
+      <c r="O40">
         <v>39</v>
       </c>
-      <c r="M40">
+      <c r="P40">
         <v>57</v>
       </c>
-      <c r="N40">
+      <c r="Q40">
         <v>52</v>
       </c>
-      <c r="O40">
+      <c r="R40">
         <v>634</v>
       </c>
-      <c r="P40">
+      <c r="S40">
         <v>786</v>
       </c>
-      <c r="Q40">
+      <c r="T40">
         <v>780</v>
       </c>
-      <c r="R40">
+      <c r="U40">
         <v>59</v>
       </c>
-      <c r="S40">
+      <c r="V40">
         <v>3694</v>
       </c>
-      <c r="T40">
+      <c r="W40">
         <v>3042</v>
       </c>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>26</v>
       </c>
@@ -2975,59 +3473,71 @@
       <c r="C41" t="s">
         <v>21</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="1">
+        <f t="shared" si="0"/>
+        <v>1000.8988764044943</v>
+      </c>
+      <c r="E41" s="1">
+        <f t="shared" si="1"/>
+        <v>551.79775280898878</v>
+      </c>
+      <c r="F41">
         <v>89</v>
       </c>
-      <c r="E41">
+      <c r="G41" s="1">
         <v>2.44</v>
       </c>
-      <c r="F41">
+      <c r="H41" s="1">
         <v>39.97</v>
       </c>
-      <c r="G41">
+      <c r="I41" s="1">
+        <f t="shared" si="2"/>
+        <v>35.605276000000003</v>
+      </c>
+      <c r="J41">
         <v>49.11</v>
       </c>
-      <c r="H41">
+      <c r="K41">
         <v>51.56</v>
       </c>
-      <c r="I41">
+      <c r="L41">
         <v>4536</v>
       </c>
-      <c r="J41">
+      <c r="M41">
         <v>4541</v>
       </c>
-      <c r="K41">
+      <c r="N41">
         <v>4539</v>
       </c>
-      <c r="L41">
+      <c r="O41">
         <v>57</v>
       </c>
-      <c r="M41">
+      <c r="P41">
         <v>58</v>
       </c>
-      <c r="N41">
+      <c r="Q41">
         <v>57</v>
       </c>
-      <c r="O41">
+      <c r="R41">
         <v>787</v>
       </c>
-      <c r="P41">
+      <c r="S41">
         <v>788</v>
       </c>
-      <c r="Q41">
+      <c r="T41">
         <v>788</v>
       </c>
-      <c r="R41">
+      <c r="U41">
         <v>3691</v>
       </c>
-      <c r="S41">
+      <c r="V41">
         <v>3696</v>
       </c>
-      <c r="T41">
+      <c r="W41">
         <v>3694</v>
       </c>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -3037,59 +3547,71 @@
       <c r="C42" t="s">
         <v>21</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="1">
+        <f t="shared" si="0"/>
+        <v>530.5913978494624</v>
+      </c>
+      <c r="E42" s="1">
+        <f t="shared" si="1"/>
+        <v>316.93548387096774</v>
+      </c>
+      <c r="F42">
         <v>186</v>
       </c>
-      <c r="E42">
+      <c r="G42" s="1">
         <v>2.4300000000000002</v>
       </c>
-      <c r="F42">
+      <c r="H42" s="1">
         <v>39.74</v>
       </c>
-      <c r="G42">
+      <c r="I42" s="1">
+        <f t="shared" si="2"/>
+        <v>39.219405999999999</v>
+      </c>
+      <c r="J42">
         <v>58.95</v>
       </c>
-      <c r="H42">
+      <c r="K42">
         <v>61.38</v>
       </c>
-      <c r="I42">
+      <c r="L42">
         <v>4544</v>
       </c>
-      <c r="J42">
+      <c r="M42">
         <v>4547</v>
       </c>
-      <c r="K42">
+      <c r="N42">
         <v>4545</v>
       </c>
-      <c r="L42">
+      <c r="O42">
         <v>58</v>
       </c>
-      <c r="M42">
+      <c r="P42">
         <v>59</v>
       </c>
-      <c r="N42">
+      <c r="Q42">
         <v>58</v>
       </c>
-      <c r="O42">
+      <c r="R42">
         <v>789</v>
       </c>
-      <c r="P42">
+      <c r="S42">
         <v>790</v>
       </c>
-      <c r="Q42">
+      <c r="T42">
         <v>790</v>
       </c>
-      <c r="R42">
+      <c r="U42">
         <v>3697</v>
       </c>
-      <c r="S42">
+      <c r="V42">
         <v>3699</v>
       </c>
-      <c r="T42">
+      <c r="W42">
         <v>3698</v>
       </c>
     </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>26</v>
       </c>
@@ -3099,59 +3621,71 @@
       <c r="C43" t="s">
         <v>21</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="1">
+        <f t="shared" si="0"/>
+        <v>882.46913580246917</v>
+      </c>
+      <c r="E43" s="1">
+        <f t="shared" si="1"/>
+        <v>493.33333333333331</v>
+      </c>
+      <c r="F43">
         <v>81</v>
       </c>
-      <c r="E43">
+      <c r="G43" s="1">
         <v>2.52</v>
       </c>
-      <c r="F43">
+      <c r="H43" s="1">
         <v>31.52</v>
       </c>
-      <c r="G43">
+      <c r="I43" s="1">
+        <f t="shared" si="2"/>
+        <v>22.530495999999999</v>
+      </c>
+      <c r="J43">
         <v>39.96</v>
       </c>
-      <c r="H43">
+      <c r="K43">
         <v>42.48</v>
       </c>
-      <c r="I43">
+      <c r="L43">
         <v>4550</v>
       </c>
-      <c r="J43">
+      <c r="M43">
         <v>4555</v>
       </c>
-      <c r="K43">
+      <c r="N43">
         <v>4552</v>
       </c>
-      <c r="L43">
+      <c r="O43">
         <v>58</v>
       </c>
-      <c r="M43">
+      <c r="P43">
         <v>60</v>
       </c>
-      <c r="N43">
+      <c r="Q43">
         <v>59</v>
       </c>
-      <c r="O43">
+      <c r="R43">
         <v>792</v>
       </c>
-      <c r="P43">
+      <c r="S43">
         <v>793</v>
       </c>
-      <c r="Q43">
+      <c r="T43">
         <v>793</v>
       </c>
-      <c r="R43">
+      <c r="U43">
         <v>3699</v>
       </c>
-      <c r="S43">
+      <c r="V43">
         <v>3703</v>
       </c>
-      <c r="T43">
+      <c r="W43">
         <v>3701</v>
       </c>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>26</v>
       </c>
@@ -3161,59 +3695,71 @@
       <c r="C44" t="s">
         <v>21</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="1">
+        <f t="shared" si="0"/>
+        <v>952.53521126760563</v>
+      </c>
+      <c r="E44" s="1">
+        <f t="shared" si="1"/>
+        <v>528.16901408450701</v>
+      </c>
+      <c r="F44">
         <v>71</v>
       </c>
-      <c r="E44">
+      <c r="G44" s="1">
         <v>2.46</v>
       </c>
-      <c r="F44">
+      <c r="H44" s="1">
         <v>30.13</v>
       </c>
-      <c r="G44">
+      <c r="I44" s="1">
+        <f t="shared" si="2"/>
+        <v>20.376918999999997</v>
+      </c>
+      <c r="J44">
         <v>37.5</v>
       </c>
-      <c r="H44">
+      <c r="K44">
         <v>39.96</v>
       </c>
-      <c r="I44">
+      <c r="L44">
         <v>4459</v>
       </c>
-      <c r="J44">
+      <c r="M44">
         <v>4562</v>
       </c>
-      <c r="K44">
+      <c r="N44">
         <v>4556</v>
       </c>
-      <c r="L44">
+      <c r="O44">
         <v>58</v>
       </c>
-      <c r="M44">
+      <c r="P44">
         <v>60</v>
       </c>
-      <c r="N44">
+      <c r="Q44">
         <v>59</v>
       </c>
-      <c r="O44">
+      <c r="R44">
         <v>795</v>
       </c>
-      <c r="P44">
+      <c r="S44">
         <v>795</v>
       </c>
-      <c r="Q44">
+      <c r="T44">
         <v>795</v>
       </c>
-      <c r="R44">
+      <c r="U44">
         <v>3605</v>
       </c>
-      <c r="S44">
+      <c r="V44">
         <v>3707</v>
       </c>
-      <c r="T44">
+      <c r="W44">
         <v>3703</v>
       </c>
     </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>26</v>
       </c>
@@ -3223,59 +3769,71 @@
       <c r="C45" t="s">
         <v>21</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="1">
+        <f t="shared" si="0"/>
+        <v>1093.3333333333333</v>
+      </c>
+      <c r="E45" s="1">
+        <f t="shared" si="1"/>
+        <v>599.10256410256409</v>
+      </c>
+      <c r="F45">
         <v>78</v>
       </c>
-      <c r="E45">
+      <c r="G45" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F45">
+      <c r="H45" s="1">
         <v>38.549999999999997</v>
       </c>
-      <c r="G45">
+      <c r="I45" s="1">
+        <f t="shared" si="2"/>
+        <v>32.875439999999998</v>
+      </c>
+      <c r="J45">
         <v>46.73</v>
       </c>
-      <c r="H45">
+      <c r="K45">
         <v>49.18</v>
       </c>
-      <c r="I45">
+      <c r="L45">
         <v>4562</v>
       </c>
-      <c r="J45">
+      <c r="M45">
         <v>4582</v>
       </c>
-      <c r="K45">
+      <c r="N45">
         <v>4569</v>
       </c>
-      <c r="L45">
+      <c r="O45">
         <v>59</v>
       </c>
-      <c r="M45">
+      <c r="P45">
         <v>67</v>
       </c>
-      <c r="N45">
+      <c r="Q45">
         <v>61</v>
       </c>
-      <c r="O45">
+      <c r="R45">
         <v>797</v>
       </c>
-      <c r="P45">
+      <c r="S45">
         <v>798</v>
       </c>
-      <c r="Q45">
+      <c r="T45">
         <v>798</v>
       </c>
-      <c r="R45">
+      <c r="U45">
         <v>3706</v>
       </c>
-      <c r="S45">
+      <c r="V45">
         <v>3717</v>
       </c>
-      <c r="T45">
+      <c r="W45">
         <v>3710</v>
       </c>
     </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -3285,59 +3843,71 @@
       <c r="C46" t="s">
         <v>21</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="1">
+        <f t="shared" si="0"/>
+        <v>382.49240121580544</v>
+      </c>
+      <c r="E46" s="1">
+        <f t="shared" si="1"/>
+        <v>244.52887537993922</v>
+      </c>
+      <c r="F46">
         <v>329</v>
       </c>
-      <c r="E46">
+      <c r="G46" s="1">
         <v>2.44</v>
       </c>
-      <c r="F46">
+      <c r="H46" s="1">
         <v>45.39</v>
       </c>
-      <c r="G46">
+      <c r="I46" s="1">
+        <f t="shared" si="2"/>
+        <v>57.118775999999997</v>
+      </c>
+      <c r="J46">
         <v>80.45</v>
       </c>
-      <c r="H46">
+      <c r="K46">
         <v>82.89</v>
       </c>
-      <c r="I46">
+      <c r="L46">
         <v>4577</v>
       </c>
-      <c r="J46">
+      <c r="M46">
         <v>4580</v>
       </c>
-      <c r="K46">
+      <c r="N46">
         <v>4578</v>
       </c>
-      <c r="L46">
+      <c r="O46">
         <v>63</v>
       </c>
-      <c r="M46">
+      <c r="P46">
         <v>64</v>
       </c>
-      <c r="N46">
+      <c r="Q46">
         <v>63</v>
       </c>
-      <c r="O46">
+      <c r="R46">
         <v>800</v>
       </c>
-      <c r="P46">
+      <c r="S46">
         <v>801</v>
       </c>
-      <c r="Q46">
+      <c r="T46">
         <v>801</v>
       </c>
-      <c r="R46">
+      <c r="U46">
         <v>3713</v>
       </c>
-      <c r="S46">
+      <c r="V46">
         <v>3716</v>
       </c>
-      <c r="T46">
+      <c r="W46">
         <v>3714</v>
       </c>
     </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>26</v>
       </c>
@@ -3347,59 +3917,71 @@
       <c r="C47" t="s">
         <v>21</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="1">
+        <f t="shared" si="0"/>
+        <v>376.44295302013415</v>
+      </c>
+      <c r="E47" s="1">
+        <f t="shared" si="1"/>
+        <v>240.83892617449663</v>
+      </c>
+      <c r="F47">
         <v>298</v>
       </c>
-      <c r="E47">
+      <c r="G47" s="1">
         <v>2.48</v>
       </c>
-      <c r="F47">
+      <c r="H47" s="1">
         <v>40.409999999999997</v>
       </c>
-      <c r="G47">
+      <c r="I47" s="1">
+        <f t="shared" si="2"/>
+        <v>45.331937999999994</v>
+      </c>
+      <c r="J47">
         <v>71.77</v>
       </c>
-      <c r="H47">
+      <c r="K47">
         <v>74.239999999999995</v>
       </c>
-      <c r="I47">
+      <c r="L47">
         <v>4582</v>
       </c>
-      <c r="J47">
+      <c r="M47">
         <v>4593</v>
       </c>
-      <c r="K47">
+      <c r="N47">
         <v>4584</v>
       </c>
-      <c r="L47">
+      <c r="O47">
         <v>64</v>
       </c>
-      <c r="M47">
+      <c r="P47">
         <v>69</v>
       </c>
-      <c r="N47">
+      <c r="Q47">
         <v>64</v>
       </c>
-      <c r="O47">
+      <c r="R47">
         <v>803</v>
       </c>
-      <c r="P47">
+      <c r="S47">
         <v>803</v>
       </c>
-      <c r="Q47">
+      <c r="T47">
         <v>803</v>
       </c>
-      <c r="R47">
+      <c r="U47">
         <v>3716</v>
       </c>
-      <c r="S47">
+      <c r="V47">
         <v>3721</v>
       </c>
-      <c r="T47">
+      <c r="W47">
         <v>3717</v>
       </c>
     </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>27</v>
       </c>
@@ -3409,59 +3991,71 @@
       <c r="C48" t="s">
         <v>28</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="1">
+        <f t="shared" si="0"/>
+        <v>2287.6315789473683</v>
+      </c>
+      <c r="E48" s="1">
+        <f t="shared" si="1"/>
+        <v>1196.3157894736842</v>
+      </c>
+      <c r="F48">
         <v>38</v>
       </c>
-      <c r="E48">
+      <c r="G48" s="1">
         <v>6.96</v>
       </c>
-      <c r="F48">
+      <c r="H48" s="1">
         <v>41.47</v>
       </c>
-      <c r="G48">
+      <c r="I48" s="1">
+        <f t="shared" si="2"/>
+        <v>36.049871000000003</v>
+      </c>
+      <c r="J48">
         <v>45.46</v>
       </c>
-      <c r="H48">
+      <c r="K48">
         <v>52.42</v>
       </c>
-      <c r="I48">
+      <c r="L48">
         <v>732</v>
       </c>
-      <c r="J48">
+      <c r="M48">
         <v>4542</v>
       </c>
-      <c r="K48">
+      <c r="N48">
         <v>3792</v>
       </c>
-      <c r="L48">
+      <c r="O48">
         <v>39</v>
       </c>
-      <c r="M48">
+      <c r="P48">
         <v>57</v>
       </c>
-      <c r="N48">
+      <c r="Q48">
         <v>51</v>
       </c>
-      <c r="O48">
+      <c r="R48">
         <v>633</v>
       </c>
-      <c r="P48">
+      <c r="S48">
         <v>785</v>
       </c>
-      <c r="Q48">
+      <c r="T48">
         <v>779</v>
       </c>
-      <c r="R48">
+      <c r="U48">
         <v>60</v>
       </c>
-      <c r="S48">
+      <c r="V48">
         <v>3700</v>
       </c>
-      <c r="T48">
+      <c r="W48">
         <v>2961</v>
       </c>
     </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>27</v>
       </c>
@@ -3471,59 +4065,71 @@
       <c r="C49" t="s">
         <v>28</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="1">
+        <f t="shared" si="0"/>
+        <v>7925</v>
+      </c>
+      <c r="E49" s="1">
+        <f t="shared" si="1"/>
+        <v>4015</v>
+      </c>
+      <c r="F49">
         <v>10</v>
       </c>
-      <c r="E49">
+      <c r="G49" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F49">
+      <c r="H49" s="1">
         <v>39.1</v>
       </c>
-      <c r="G49">
+      <c r="I49" s="1">
+        <f t="shared" si="2"/>
+        <v>30.986750000000001</v>
+      </c>
+      <c r="J49">
         <v>40.15</v>
       </c>
-      <c r="H49">
+      <c r="K49">
         <v>42.62</v>
       </c>
-      <c r="I49">
+      <c r="L49">
         <v>4541</v>
       </c>
-      <c r="J49">
+      <c r="M49">
         <v>4545</v>
       </c>
-      <c r="K49">
+      <c r="N49">
         <v>4544</v>
       </c>
-      <c r="L49">
+      <c r="O49">
         <v>56</v>
       </c>
-      <c r="M49">
+      <c r="P49">
         <v>58</v>
       </c>
-      <c r="N49">
+      <c r="Q49">
         <v>56</v>
       </c>
-      <c r="O49">
+      <c r="R49">
         <v>787</v>
       </c>
-      <c r="P49">
+      <c r="S49">
         <v>787</v>
       </c>
-      <c r="Q49">
+      <c r="T49">
         <v>787</v>
       </c>
-      <c r="R49">
+      <c r="U49">
         <v>3698</v>
       </c>
-      <c r="S49">
+      <c r="V49">
         <v>3702</v>
       </c>
-      <c r="T49">
+      <c r="W49">
         <v>3700</v>
       </c>
     </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>27</v>
       </c>
@@ -3533,59 +4139,71 @@
       <c r="C50" t="s">
         <v>28</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="1">
+        <f t="shared" si="0"/>
+        <v>1035.4216867469879</v>
+      </c>
+      <c r="E50" s="1">
+        <f t="shared" si="1"/>
+        <v>569.03614457831327</v>
+      </c>
+      <c r="F50">
         <v>83</v>
       </c>
-      <c r="E50">
+      <c r="G50" s="1">
         <v>2.46</v>
       </c>
-      <c r="F50">
+      <c r="H50" s="1">
         <v>38.71</v>
       </c>
-      <c r="G50">
+      <c r="I50" s="1">
+        <f t="shared" si="2"/>
+        <v>33.267373999999997</v>
+      </c>
+      <c r="J50">
         <v>47.23</v>
       </c>
-      <c r="H50">
+      <c r="K50">
         <v>49.69</v>
       </c>
-      <c r="I50">
+      <c r="L50">
         <v>4495</v>
       </c>
-      <c r="J50">
+      <c r="M50">
         <v>4555</v>
       </c>
-      <c r="K50">
+      <c r="N50">
         <v>4550</v>
       </c>
-      <c r="L50">
+      <c r="O50">
         <v>57</v>
       </c>
-      <c r="M50">
+      <c r="P50">
         <v>59</v>
       </c>
-      <c r="N50">
+      <c r="Q50">
         <v>57</v>
       </c>
-      <c r="O50">
+      <c r="R50">
         <v>789</v>
       </c>
-      <c r="P50">
+      <c r="S50">
         <v>789</v>
       </c>
-      <c r="Q50">
+      <c r="T50">
         <v>789</v>
       </c>
-      <c r="R50">
+      <c r="U50">
         <v>3649</v>
       </c>
-      <c r="S50">
+      <c r="V50">
         <v>3707</v>
       </c>
-      <c r="T50">
+      <c r="W50">
         <v>3703</v>
       </c>
     </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>27</v>
       </c>
@@ -3595,59 +4213,71 @@
       <c r="C51" t="s">
         <v>28</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="1">
+        <f t="shared" si="0"/>
+        <v>2018.3783783783783</v>
+      </c>
+      <c r="E51" s="1">
+        <f t="shared" si="1"/>
+        <v>1060.8108108108108</v>
+      </c>
+      <c r="F51">
         <v>37</v>
       </c>
-      <c r="E51">
+      <c r="G51" s="1">
         <v>2.54</v>
       </c>
-      <c r="F51">
+      <c r="H51" s="1">
         <v>35.43</v>
       </c>
-      <c r="G51">
+      <c r="I51" s="1">
+        <f t="shared" si="2"/>
+        <v>26.459123999999999</v>
+      </c>
+      <c r="J51">
         <v>39.25</v>
       </c>
-      <c r="H51">
+      <c r="K51">
         <v>41.78</v>
       </c>
-      <c r="I51">
+      <c r="L51">
         <v>4555</v>
       </c>
-      <c r="J51">
+      <c r="M51">
         <v>4559</v>
       </c>
-      <c r="K51">
+      <c r="N51">
         <v>4557</v>
       </c>
-      <c r="L51">
+      <c r="O51">
         <v>57</v>
       </c>
-      <c r="M51">
+      <c r="P51">
         <v>58</v>
       </c>
-      <c r="N51">
+      <c r="Q51">
         <v>58</v>
       </c>
-      <c r="O51">
+      <c r="R51">
         <v>791</v>
       </c>
-      <c r="P51">
+      <c r="S51">
         <v>792</v>
       </c>
-      <c r="Q51">
+      <c r="T51">
         <v>792</v>
       </c>
-      <c r="R51">
+      <c r="U51">
         <v>3706</v>
       </c>
-      <c r="S51">
+      <c r="V51">
         <v>3709</v>
       </c>
-      <c r="T51">
+      <c r="W51">
         <v>3707</v>
       </c>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>27</v>
       </c>
@@ -3657,59 +4287,71 @@
       <c r="C52" t="s">
         <v>28</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="1">
+        <f t="shared" si="0"/>
+        <v>39084.999999999993</v>
+      </c>
+      <c r="E52" s="1">
+        <f t="shared" si="1"/>
+        <v>19595</v>
+      </c>
+      <c r="F52">
         <v>2</v>
       </c>
-      <c r="E52">
+      <c r="G52" s="1">
         <v>2.46</v>
       </c>
-      <c r="F52">
+      <c r="H52" s="1">
         <v>38.979999999999997</v>
       </c>
-      <c r="G52">
+      <c r="I52" s="1">
+        <f t="shared" si="2"/>
+        <v>30.470665999999991</v>
+      </c>
+      <c r="J52">
         <v>39.19</v>
       </c>
-      <c r="H52">
+      <c r="K52">
         <v>41.65</v>
       </c>
-      <c r="I52">
+      <c r="L52">
         <v>4563</v>
       </c>
-      <c r="J52">
+      <c r="M52">
         <v>4571</v>
       </c>
-      <c r="K52">
+      <c r="N52">
         <v>4565</v>
       </c>
-      <c r="L52">
+      <c r="O52">
         <v>58</v>
       </c>
-      <c r="M52">
+      <c r="P52">
         <v>62</v>
       </c>
-      <c r="N52">
+      <c r="Q52">
         <v>60</v>
       </c>
-      <c r="O52">
+      <c r="R52">
         <v>794</v>
       </c>
-      <c r="P52">
+      <c r="S52">
         <v>794</v>
       </c>
-      <c r="Q52">
+      <c r="T52">
         <v>794</v>
       </c>
-      <c r="R52">
+      <c r="U52">
         <v>3710</v>
       </c>
-      <c r="S52">
+      <c r="V52">
         <v>3714</v>
       </c>
-      <c r="T52">
+      <c r="W52">
         <v>3712</v>
       </c>
     </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>27</v>
       </c>
@@ -3719,59 +4361,71 @@
       <c r="C53" t="s">
         <v>28</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="1">
+        <f t="shared" si="0"/>
+        <v>1061.875</v>
+      </c>
+      <c r="E53" s="1">
+        <f t="shared" si="1"/>
+        <v>583.5</v>
+      </c>
+      <c r="F53">
         <v>80</v>
       </c>
-      <c r="E53">
+      <c r="G53" s="1">
         <v>2.42</v>
       </c>
-      <c r="F53">
+      <c r="H53" s="1">
         <v>38.270000000000003</v>
       </c>
-      <c r="G53">
+      <c r="I53" s="1">
+        <f t="shared" si="2"/>
+        <v>32.510365000000007</v>
+      </c>
+      <c r="J53">
         <v>46.68</v>
       </c>
-      <c r="H53">
+      <c r="K53">
         <v>49.1</v>
       </c>
-      <c r="I53">
+      <c r="L53">
         <v>4568</v>
       </c>
-      <c r="J53">
+      <c r="M53">
         <v>4573</v>
       </c>
-      <c r="K53">
+      <c r="N53">
         <v>4571</v>
       </c>
-      <c r="L53">
+      <c r="O53">
         <v>59</v>
       </c>
-      <c r="M53">
+      <c r="P53">
         <v>61</v>
       </c>
-      <c r="N53">
+      <c r="Q53">
         <v>60</v>
       </c>
-      <c r="O53">
+      <c r="R53">
         <v>797</v>
       </c>
-      <c r="P53">
+      <c r="S53">
         <v>797</v>
       </c>
-      <c r="Q53">
+      <c r="T53">
         <v>797</v>
       </c>
-      <c r="R53">
+      <c r="U53">
         <v>3713</v>
       </c>
-      <c r="S53">
+      <c r="V53">
         <v>3716</v>
       </c>
-      <c r="T53">
+      <c r="W53">
         <v>3715</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>27</v>
       </c>
@@ -3781,59 +4435,71 @@
       <c r="C54" t="s">
         <v>28</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="1">
+        <f t="shared" si="0"/>
+        <v>548.96174863387989</v>
+      </c>
+      <c r="E54" s="1">
+        <f t="shared" si="1"/>
+        <v>326.55737704918033</v>
+      </c>
+      <c r="F54">
         <v>183</v>
       </c>
-      <c r="E54">
+      <c r="G54" s="1">
         <v>2.42</v>
       </c>
-      <c r="F54">
+      <c r="H54" s="1">
         <v>40.700000000000003</v>
       </c>
-      <c r="G54">
+      <c r="I54" s="1">
+        <f t="shared" si="2"/>
+        <v>40.887220000000006</v>
+      </c>
+      <c r="J54">
         <v>59.76</v>
       </c>
-      <c r="H54">
+      <c r="K54">
         <v>62.18</v>
       </c>
-      <c r="I54">
+      <c r="L54">
         <v>4575</v>
       </c>
-      <c r="J54">
+      <c r="M54">
         <v>4583</v>
       </c>
-      <c r="K54">
+      <c r="N54">
         <v>4577</v>
       </c>
-      <c r="L54">
+      <c r="O54">
         <v>60</v>
       </c>
-      <c r="M54">
+      <c r="P54">
         <v>64</v>
       </c>
-      <c r="N54">
+      <c r="Q54">
         <v>60</v>
       </c>
-      <c r="O54">
+      <c r="R54">
         <v>799</v>
       </c>
-      <c r="P54">
+      <c r="S54">
         <v>799</v>
       </c>
-      <c r="Q54">
+      <c r="T54">
         <v>799</v>
       </c>
-      <c r="R54">
+      <c r="U54">
         <v>3716</v>
       </c>
-      <c r="S54">
+      <c r="V54">
         <v>3720</v>
       </c>
-      <c r="T54">
+      <c r="W54">
         <v>3718</v>
       </c>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>27</v>
       </c>
@@ -3843,59 +4509,71 @@
       <c r="C55" t="s">
         <v>28</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="1">
+        <f t="shared" si="0"/>
+        <v>6758.333333333333</v>
+      </c>
+      <c r="E55" s="1">
+        <f t="shared" si="1"/>
+        <v>3430</v>
+      </c>
+      <c r="F55">
         <v>12</v>
       </c>
-      <c r="E55">
+      <c r="G55" s="1">
         <v>2.4</v>
       </c>
-      <c r="F55">
+      <c r="H55" s="1">
         <v>39.94</v>
       </c>
-      <c r="G55">
+      <c r="I55" s="1">
+        <f t="shared" si="2"/>
+        <v>32.391339999999992</v>
+      </c>
+      <c r="J55">
         <v>41.16</v>
       </c>
-      <c r="H55">
+      <c r="K55">
         <v>43.56</v>
       </c>
-      <c r="I55">
+      <c r="L55">
         <v>4578</v>
       </c>
-      <c r="J55">
+      <c r="M55">
         <v>4590</v>
       </c>
-      <c r="K55">
+      <c r="N55">
         <v>4582</v>
       </c>
-      <c r="L55">
+      <c r="O55">
         <v>59</v>
       </c>
-      <c r="M55">
+      <c r="P55">
         <v>65</v>
       </c>
-      <c r="N55">
+      <c r="Q55">
         <v>61</v>
       </c>
-      <c r="O55">
+      <c r="R55">
         <v>801</v>
       </c>
-      <c r="P55">
+      <c r="S55">
         <v>801</v>
       </c>
-      <c r="Q55">
+      <c r="T55">
         <v>801</v>
       </c>
-      <c r="R55">
+      <c r="U55">
         <v>3718</v>
       </c>
-      <c r="S55">
+      <c r="V55">
         <v>3724</v>
       </c>
-      <c r="T55">
+      <c r="W55">
         <v>3720</v>
       </c>
     </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>29</v>
       </c>
@@ -3905,59 +4583,71 @@
       <c r="C56" t="s">
         <v>28</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="1">
+        <f t="shared" si="0"/>
+        <v>1925.6818181818178</v>
+      </c>
+      <c r="E56" s="1">
+        <f t="shared" si="1"/>
+        <v>1012.9545454545455</v>
+      </c>
+      <c r="F56">
         <v>44</v>
       </c>
-      <c r="E56">
+      <c r="G56" s="1">
         <v>7.05</v>
       </c>
-      <c r="F56">
+      <c r="H56" s="1">
         <v>40.159999999999997</v>
       </c>
-      <c r="G56">
+      <c r="I56" s="1">
+        <f t="shared" si="2"/>
+        <v>34.027567999999995</v>
+      </c>
+      <c r="J56">
         <v>44.57</v>
       </c>
-      <c r="H56">
+      <c r="K56">
         <v>51.62</v>
       </c>
-      <c r="I56">
+      <c r="L56">
         <v>734</v>
       </c>
-      <c r="J56">
+      <c r="M56">
         <v>4313</v>
       </c>
-      <c r="K56">
+      <c r="N56">
         <v>3649</v>
       </c>
-      <c r="L56">
+      <c r="O56">
         <v>39</v>
       </c>
-      <c r="M56">
+      <c r="P56">
         <v>56</v>
       </c>
-      <c r="N56">
+      <c r="Q56">
         <v>51</v>
       </c>
-      <c r="O56">
+      <c r="R56">
         <v>635</v>
       </c>
-      <c r="P56">
+      <c r="S56">
         <v>786</v>
       </c>
-      <c r="Q56">
+      <c r="T56">
         <v>780</v>
       </c>
-      <c r="R56">
+      <c r="U56">
         <v>59</v>
       </c>
-      <c r="S56">
+      <c r="V56">
         <v>3471</v>
       </c>
-      <c r="T56">
+      <c r="W56">
         <v>2818</v>
       </c>
     </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -3967,59 +4657,71 @@
       <c r="C57" t="s">
         <v>28</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="1">
+        <f t="shared" si="0"/>
+        <v>1053.125</v>
+      </c>
+      <c r="E57" s="1">
+        <f t="shared" si="1"/>
+        <v>576.25</v>
+      </c>
+      <c r="F57">
         <v>80</v>
       </c>
-      <c r="E57">
+      <c r="G57" s="1">
         <v>2.44</v>
       </c>
-      <c r="F57">
+      <c r="H57" s="1">
         <v>38.15</v>
       </c>
-      <c r="G57">
+      <c r="I57" s="1">
+        <f t="shared" si="2"/>
+        <v>32.141374999999996</v>
+      </c>
+      <c r="J57">
         <v>46.1</v>
       </c>
-      <c r="H57">
+      <c r="K57">
         <v>48.54</v>
       </c>
-      <c r="I57">
+      <c r="L57">
         <v>4313</v>
       </c>
-      <c r="J57">
+      <c r="M57">
         <v>4325</v>
       </c>
-      <c r="K57">
+      <c r="N57">
         <v>4319</v>
       </c>
-      <c r="L57">
+      <c r="O57">
         <v>56</v>
       </c>
-      <c r="M57">
+      <c r="P57">
         <v>58</v>
       </c>
-      <c r="N57">
+      <c r="Q57">
         <v>56</v>
       </c>
-      <c r="O57">
+      <c r="R57">
         <v>788</v>
       </c>
-      <c r="P57">
+      <c r="S57">
         <v>788</v>
       </c>
-      <c r="Q57">
+      <c r="T57">
         <v>788</v>
       </c>
-      <c r="R57">
+      <c r="U57">
         <v>3468</v>
       </c>
-      <c r="S57">
+      <c r="V57">
         <v>3478</v>
       </c>
-      <c r="T57">
+      <c r="W57">
         <v>3474</v>
       </c>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>29</v>
       </c>
@@ -4029,59 +4731,71 @@
       <c r="C58" t="s">
         <v>28</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="1">
+        <f t="shared" si="0"/>
+        <v>1101.5277777777778</v>
+      </c>
+      <c r="E58" s="1">
+        <f t="shared" si="1"/>
+        <v>600.41666666666663</v>
+      </c>
+      <c r="F58">
         <v>72</v>
       </c>
-      <c r="E58">
+      <c r="G58" s="1">
         <v>2.38</v>
       </c>
-      <c r="F58">
+      <c r="H58" s="1">
         <v>36.08</v>
       </c>
-      <c r="G58">
+      <c r="I58" s="1">
+        <f t="shared" si="2"/>
+        <v>28.615047999999998</v>
+      </c>
+      <c r="J58">
         <v>43.23</v>
       </c>
-      <c r="H58">
+      <c r="K58">
         <v>45.62</v>
       </c>
-      <c r="I58">
+      <c r="L58">
         <v>4323</v>
       </c>
-      <c r="J58">
+      <c r="M58">
         <v>4327</v>
       </c>
-      <c r="K58">
+      <c r="N58">
         <v>4325</v>
       </c>
-      <c r="L58">
+      <c r="O58">
         <v>56</v>
       </c>
-      <c r="M58">
+      <c r="P58">
         <v>57</v>
       </c>
-      <c r="N58">
+      <c r="Q58">
         <v>57</v>
       </c>
-      <c r="O58">
+      <c r="R58">
         <v>790</v>
       </c>
-      <c r="P58">
+      <c r="S58">
         <v>791</v>
       </c>
-      <c r="Q58">
+      <c r="T58">
         <v>791</v>
       </c>
-      <c r="R58">
+      <c r="U58">
         <v>3477</v>
       </c>
-      <c r="S58">
+      <c r="V58">
         <v>3480</v>
       </c>
-      <c r="T58">
+      <c r="W58">
         <v>3478</v>
       </c>
     </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>29</v>
       </c>
@@ -4091,59 +4805,71 @@
       <c r="C59" t="s">
         <v>28</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="1">
+        <f t="shared" si="0"/>
+        <v>1776.75</v>
+      </c>
+      <c r="E59" s="1">
+        <f t="shared" si="1"/>
+        <v>938</v>
+      </c>
+      <c r="F59">
         <v>40</v>
       </c>
-      <c r="E59">
+      <c r="G59" s="1">
         <v>2.4</v>
       </c>
-      <c r="F59">
+      <c r="H59" s="1">
         <v>33.549999999999997</v>
       </c>
-      <c r="G59">
+      <c r="I59" s="1">
+        <f t="shared" si="2"/>
+        <v>23.843984999999993</v>
+      </c>
+      <c r="J59">
         <v>37.520000000000003</v>
       </c>
-      <c r="H59">
+      <c r="K59">
         <v>39.92</v>
       </c>
-      <c r="I59">
+      <c r="L59">
         <v>4329</v>
       </c>
-      <c r="J59">
+      <c r="M59">
         <v>4332</v>
       </c>
-      <c r="K59">
+      <c r="N59">
         <v>4330</v>
       </c>
-      <c r="L59">
+      <c r="O59">
         <v>56</v>
       </c>
-      <c r="M59">
+      <c r="P59">
         <v>57</v>
       </c>
-      <c r="N59">
+      <c r="Q59">
         <v>57</v>
       </c>
-      <c r="O59">
+      <c r="R59">
         <v>793</v>
       </c>
-      <c r="P59">
+      <c r="S59">
         <v>793</v>
       </c>
-      <c r="Q59">
+      <c r="T59">
         <v>793</v>
       </c>
-      <c r="R59">
+      <c r="U59">
         <v>3480</v>
       </c>
-      <c r="S59">
+      <c r="V59">
         <v>3482</v>
       </c>
-      <c r="T59">
+      <c r="W59">
         <v>3480</v>
       </c>
     </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>29</v>
       </c>
@@ -4153,59 +4879,71 @@
       <c r="C60" t="s">
         <v>28</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="1">
+        <f t="shared" si="0"/>
+        <v>1671.5217391304348</v>
+      </c>
+      <c r="E60" s="1">
+        <f t="shared" si="1"/>
+        <v>885.86956521739125</v>
+      </c>
+      <c r="F60">
         <v>46</v>
       </c>
-      <c r="E60">
+      <c r="G60" s="1">
         <v>2.46</v>
       </c>
-      <c r="F60">
+      <c r="H60" s="1">
         <v>36.14</v>
       </c>
-      <c r="G60">
+      <c r="I60" s="1">
+        <f t="shared" si="2"/>
+        <v>27.788046000000001</v>
+      </c>
+      <c r="J60">
         <v>40.75</v>
       </c>
-      <c r="H60">
+      <c r="K60">
         <v>43.2</v>
       </c>
-      <c r="I60">
+      <c r="L60">
         <v>4335</v>
       </c>
-      <c r="J60">
+      <c r="M60">
         <v>4339</v>
       </c>
-      <c r="K60">
+      <c r="N60">
         <v>4336</v>
       </c>
-      <c r="L60">
+      <c r="O60">
         <v>57</v>
       </c>
-      <c r="M60">
+      <c r="P60">
         <v>58</v>
       </c>
-      <c r="N60">
+      <c r="Q60">
         <v>57</v>
       </c>
-      <c r="O60">
+      <c r="R60">
         <v>795</v>
       </c>
-      <c r="P60">
+      <c r="S60">
         <v>795</v>
       </c>
-      <c r="Q60">
+      <c r="T60">
         <v>795</v>
       </c>
-      <c r="R60">
+      <c r="U60">
         <v>3483</v>
       </c>
-      <c r="S60">
+      <c r="V60">
         <v>3486</v>
       </c>
-      <c r="T60">
+      <c r="W60">
         <v>3483</v>
       </c>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>29</v>
       </c>
@@ -4215,59 +4953,71 @@
       <c r="C61" t="s">
         <v>28</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="1">
+        <f t="shared" si="0"/>
+        <v>374.40433212996396</v>
+      </c>
+      <c r="E61" s="1">
+        <f t="shared" si="1"/>
+        <v>237.76173285198556</v>
+      </c>
+      <c r="F61">
         <v>277</v>
       </c>
-      <c r="E61">
+      <c r="G61" s="1">
         <v>2.42</v>
       </c>
-      <c r="F61">
+      <c r="H61" s="1">
         <v>37.85</v>
       </c>
-      <c r="G61">
+      <c r="I61" s="1">
+        <f t="shared" si="2"/>
+        <v>39.254235000000008</v>
+      </c>
+      <c r="J61">
         <v>65.86</v>
       </c>
-      <c r="H61">
+      <c r="K61">
         <v>68.28</v>
       </c>
-      <c r="I61">
+      <c r="L61">
         <v>4340</v>
       </c>
-      <c r="J61">
+      <c r="M61">
         <v>4344</v>
       </c>
-      <c r="K61">
+      <c r="N61">
         <v>4342</v>
       </c>
-      <c r="L61">
+      <c r="O61">
         <v>57</v>
       </c>
-      <c r="M61">
+      <c r="P61">
         <v>59</v>
       </c>
-      <c r="N61">
+      <c r="Q61">
         <v>58</v>
       </c>
-      <c r="O61">
+      <c r="R61">
         <v>797</v>
       </c>
-      <c r="P61">
+      <c r="S61">
         <v>798</v>
       </c>
-      <c r="Q61">
+      <c r="T61">
         <v>798</v>
       </c>
-      <c r="R61">
+      <c r="U61">
         <v>3485</v>
       </c>
-      <c r="S61">
+      <c r="V61">
         <v>3487</v>
       </c>
-      <c r="T61">
+      <c r="W61">
         <v>3486</v>
       </c>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>29</v>
       </c>
@@ -4277,59 +5027,71 @@
       <c r="C62" t="s">
         <v>28</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="1">
+        <f t="shared" si="0"/>
+        <v>3174.1666666666665</v>
+      </c>
+      <c r="E62" s="1">
+        <f t="shared" si="1"/>
+        <v>1637.5</v>
+      </c>
+      <c r="F62">
         <v>24</v>
       </c>
-      <c r="E62">
+      <c r="G62" s="1">
         <v>2.5</v>
       </c>
-      <c r="F62">
+      <c r="H62" s="1">
         <v>36.880000000000003</v>
       </c>
-      <c r="G62">
+      <c r="I62" s="1">
+        <f t="shared" si="2"/>
+        <v>28.095184000000003</v>
+      </c>
+      <c r="J62">
         <v>39.299999999999997</v>
       </c>
-      <c r="H62">
+      <c r="K62">
         <v>41.8</v>
       </c>
-      <c r="I62">
+      <c r="L62">
         <v>4307</v>
       </c>
-      <c r="J62">
+      <c r="M62">
         <v>4355</v>
       </c>
-      <c r="K62">
+      <c r="N62">
         <v>4348</v>
       </c>
-      <c r="L62">
+      <c r="O62">
         <v>58</v>
       </c>
-      <c r="M62">
+      <c r="P62">
         <v>62</v>
       </c>
-      <c r="N62">
+      <c r="Q62">
         <v>58</v>
       </c>
-      <c r="O62">
+      <c r="R62">
         <v>800</v>
       </c>
-      <c r="P62">
+      <c r="S62">
         <v>801</v>
       </c>
-      <c r="Q62">
+      <c r="T62">
         <v>801</v>
       </c>
-      <c r="R62">
+      <c r="U62">
         <v>3445</v>
       </c>
-      <c r="S62">
+      <c r="V62">
         <v>3492</v>
       </c>
-      <c r="T62">
+      <c r="W62">
         <v>3488</v>
       </c>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>29</v>
       </c>
@@ -4339,59 +5101,71 @@
       <c r="C63" t="s">
         <v>28</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="1">
+        <f t="shared" si="0"/>
+        <v>3376.9565217391296</v>
+      </c>
+      <c r="E63" s="1">
+        <f t="shared" si="1"/>
+        <v>1738.2608695652175</v>
+      </c>
+      <c r="F63">
         <v>23</v>
       </c>
-      <c r="E63">
+      <c r="G63" s="1">
         <v>2.44</v>
       </c>
-      <c r="F63">
+      <c r="H63" s="1">
         <v>37.69</v>
       </c>
-      <c r="G63">
+      <c r="I63" s="1">
+        <f t="shared" si="2"/>
+        <v>29.273822999999993</v>
+      </c>
+      <c r="J63">
         <v>39.979999999999997</v>
       </c>
-      <c r="H63">
+      <c r="K63">
         <v>42.42</v>
       </c>
-      <c r="I63">
+      <c r="L63">
         <v>4352</v>
       </c>
-      <c r="J63">
+      <c r="M63">
         <v>4362</v>
       </c>
-      <c r="K63">
+      <c r="N63">
         <v>4353</v>
       </c>
-      <c r="L63">
+      <c r="O63">
         <v>58</v>
       </c>
-      <c r="M63">
+      <c r="P63">
         <v>63</v>
       </c>
-      <c r="N63">
+      <c r="Q63">
         <v>59</v>
       </c>
-      <c r="O63">
+      <c r="R63">
         <v>803</v>
       </c>
-      <c r="P63">
+      <c r="S63">
         <v>803</v>
       </c>
-      <c r="Q63">
+      <c r="T63">
         <v>803</v>
       </c>
-      <c r="R63">
+      <c r="U63">
         <v>3491</v>
       </c>
-      <c r="S63">
+      <c r="V63">
         <v>3496</v>
       </c>
-      <c r="T63">
+      <c r="W63">
         <v>3492</v>
       </c>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>30</v>
       </c>
@@ -4401,59 +5175,71 @@
       <c r="C64" t="s">
         <v>28</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="1">
+        <f t="shared" si="0"/>
+        <v>2289.4736842105262</v>
+      </c>
+      <c r="E64" s="1">
+        <f t="shared" si="1"/>
+        <v>1194.4736842105262</v>
+      </c>
+      <c r="F64">
         <v>38</v>
       </c>
-      <c r="E64">
+      <c r="G64" s="1">
         <v>6.87</v>
       </c>
-      <c r="F64">
+      <c r="H64" s="1">
         <v>41.61</v>
       </c>
-      <c r="G64">
+      <c r="I64" s="1">
+        <f t="shared" si="2"/>
+        <v>36.200699999999998</v>
+      </c>
+      <c r="J64">
         <v>45.39</v>
       </c>
-      <c r="H64">
+      <c r="K64">
         <v>52.26</v>
       </c>
-      <c r="I64">
+      <c r="L64">
         <v>734</v>
       </c>
-      <c r="J64">
+      <c r="M64">
         <v>4339</v>
       </c>
-      <c r="K64">
+      <c r="N64">
         <v>3681</v>
       </c>
-      <c r="L64">
+      <c r="O64">
         <v>39</v>
       </c>
-      <c r="M64">
+      <c r="P64">
         <v>57</v>
       </c>
-      <c r="N64">
+      <c r="Q64">
         <v>51</v>
       </c>
-      <c r="O64">
+      <c r="R64">
         <v>635</v>
       </c>
-      <c r="P64">
+      <c r="S64">
         <v>787</v>
       </c>
-      <c r="Q64">
+      <c r="T64">
         <v>780</v>
       </c>
-      <c r="R64">
+      <c r="U64">
         <v>60</v>
       </c>
-      <c r="S64">
+      <c r="V64">
         <v>3495</v>
       </c>
-      <c r="T64">
+      <c r="W64">
         <v>2849</v>
       </c>
     </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>30</v>
       </c>
@@ -4463,59 +5249,71 @@
       <c r="C65" t="s">
         <v>28</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="1">
+        <f t="shared" si="0"/>
+        <v>1236.6666666666667</v>
+      </c>
+      <c r="E65" s="1">
+        <f t="shared" si="1"/>
+        <v>668.33333333333337</v>
+      </c>
+      <c r="F65">
         <v>66</v>
       </c>
-      <c r="E65">
+      <c r="G65" s="1">
         <v>2.4300000000000002</v>
       </c>
-      <c r="F65">
+      <c r="H65" s="1">
         <v>37.51</v>
       </c>
-      <c r="G65">
+      <c r="I65" s="1">
+        <f t="shared" si="2"/>
+        <v>30.615662</v>
+      </c>
+      <c r="J65">
         <v>44.11</v>
       </c>
-      <c r="H65">
+      <c r="K65">
         <v>46.55</v>
       </c>
-      <c r="I65">
+      <c r="L65">
         <v>4338</v>
       </c>
-      <c r="J65">
+      <c r="M65">
         <v>4347</v>
       </c>
-      <c r="K65">
+      <c r="N65">
         <v>4341</v>
       </c>
-      <c r="L65">
+      <c r="O65">
         <v>57</v>
       </c>
-      <c r="M65">
+      <c r="P65">
         <v>59</v>
       </c>
-      <c r="N65">
+      <c r="Q65">
         <v>57</v>
       </c>
-      <c r="O65">
+      <c r="R65">
         <v>788</v>
       </c>
-      <c r="P65">
+      <c r="S65">
         <v>788</v>
       </c>
-      <c r="Q65">
+      <c r="T65">
         <v>788</v>
       </c>
-      <c r="R65">
+      <c r="U65">
         <v>3493</v>
       </c>
-      <c r="S65">
+      <c r="V65">
         <v>3500</v>
       </c>
-      <c r="T65">
+      <c r="W65">
         <v>3496</v>
       </c>
     </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>30</v>
       </c>
@@ -4525,59 +5323,71 @@
       <c r="C66" t="s">
         <v>28</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="1">
+        <f t="shared" si="0"/>
+        <v>890.68965517241395</v>
+      </c>
+      <c r="E66" s="1">
+        <f t="shared" si="1"/>
+        <v>495.05747126436779</v>
+      </c>
+      <c r="F66">
         <v>87</v>
       </c>
-      <c r="E66">
+      <c r="G66" s="1">
         <v>2.35</v>
       </c>
-      <c r="F66">
+      <c r="H66" s="1">
         <v>34.42</v>
       </c>
-      <c r="G66">
+      <c r="I66" s="1">
+        <f t="shared" si="2"/>
+        <v>26.672058000000007</v>
+      </c>
+      <c r="J66">
         <v>43.07</v>
       </c>
-      <c r="H66">
+      <c r="K66">
         <v>45.42</v>
       </c>
-      <c r="I66">
+      <c r="L66">
         <v>4345</v>
       </c>
-      <c r="J66">
+      <c r="M66">
         <v>4349</v>
       </c>
-      <c r="K66">
+      <c r="N66">
         <v>4347</v>
       </c>
-      <c r="L66">
+      <c r="O66">
         <v>57</v>
       </c>
-      <c r="M66">
+      <c r="P66">
         <v>58</v>
       </c>
-      <c r="N66">
+      <c r="Q66">
         <v>57</v>
       </c>
-      <c r="O66">
+      <c r="R66">
         <v>789</v>
       </c>
-      <c r="P66">
+      <c r="S66">
         <v>790</v>
       </c>
-      <c r="Q66">
+      <c r="T66">
         <v>790</v>
       </c>
-      <c r="R66">
+      <c r="U66">
         <v>3498</v>
       </c>
-      <c r="S66">
+      <c r="V66">
         <v>3502</v>
       </c>
-      <c r="T66">
+      <c r="W66">
         <v>3500</v>
       </c>
     </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -4587,59 +5397,71 @@
       <c r="C67" t="s">
         <v>28</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="1">
+        <f t="shared" ref="D67:D96" si="3">(H67+J67)*1000/F67</f>
+        <v>1186.5079365079366</v>
+      </c>
+      <c r="E67" s="1">
+        <f t="shared" ref="E67:E96" si="4">J67*1000/F67</f>
+        <v>643.49206349206349</v>
+      </c>
+      <c r="F67">
         <v>63</v>
       </c>
-      <c r="E67">
+      <c r="G67" s="1">
         <v>2.4300000000000002</v>
       </c>
-      <c r="F67">
+      <c r="H67" s="1">
         <v>34.21</v>
       </c>
-      <c r="G67">
+      <c r="I67" s="1">
+        <f t="shared" ref="I67:I96" si="5">(H67+J67)/100*H67</f>
+        <v>25.571975000000002</v>
+      </c>
+      <c r="J67">
         <v>40.54</v>
       </c>
-      <c r="H67">
+      <c r="K67">
         <v>42.97</v>
       </c>
-      <c r="I67">
+      <c r="L67">
         <v>4352</v>
       </c>
-      <c r="J67">
+      <c r="M67">
         <v>4355</v>
       </c>
-      <c r="K67">
+      <c r="N67">
         <v>4353</v>
       </c>
-      <c r="L67">
+      <c r="O67">
         <v>57</v>
       </c>
-      <c r="M67">
+      <c r="P67">
         <v>59</v>
       </c>
-      <c r="N67">
+      <c r="Q67">
         <v>58</v>
       </c>
-      <c r="O67">
+      <c r="R67">
         <v>792</v>
       </c>
-      <c r="P67">
+      <c r="S67">
         <v>792</v>
       </c>
-      <c r="Q67">
+      <c r="T67">
         <v>792</v>
       </c>
-      <c r="R67">
+      <c r="U67">
         <v>3502</v>
       </c>
-      <c r="S67">
+      <c r="V67">
         <v>3505</v>
       </c>
-      <c r="T67">
+      <c r="W67">
         <v>3503</v>
       </c>
     </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>30</v>
       </c>
@@ -4649,59 +5471,71 @@
       <c r="C68" t="s">
         <v>28</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="1">
+        <f t="shared" si="3"/>
+        <v>3138.695652173913</v>
+      </c>
+      <c r="E68" s="1">
+        <f t="shared" si="4"/>
+        <v>1620</v>
+      </c>
+      <c r="F68">
         <v>23</v>
       </c>
-      <c r="E68">
+      <c r="G68" s="1">
         <v>2.5</v>
       </c>
-      <c r="F68">
+      <c r="H68" s="1">
         <v>34.93</v>
       </c>
-      <c r="G68">
+      <c r="I68" s="1">
+        <f t="shared" si="5"/>
+        <v>25.215966999999999</v>
+      </c>
+      <c r="J68">
         <v>37.26</v>
       </c>
-      <c r="H68">
+      <c r="K68">
         <v>39.76</v>
       </c>
-      <c r="I68">
+      <c r="L68">
         <v>4359</v>
       </c>
-      <c r="J68">
+      <c r="M68">
         <v>4372</v>
       </c>
-      <c r="K68">
+      <c r="N68">
         <v>4363</v>
       </c>
-      <c r="L68">
+      <c r="O68">
         <v>58</v>
       </c>
-      <c r="M68">
+      <c r="P68">
         <v>63</v>
       </c>
-      <c r="N68">
+      <c r="Q68">
         <v>60</v>
       </c>
-      <c r="O68">
+      <c r="R68">
         <v>795</v>
       </c>
-      <c r="P68">
+      <c r="S68">
         <v>795</v>
       </c>
-      <c r="Q68">
+      <c r="T68">
         <v>795</v>
       </c>
-      <c r="R68">
+      <c r="U68">
         <v>3505</v>
       </c>
-      <c r="S68">
+      <c r="V68">
         <v>3513</v>
       </c>
-      <c r="T68">
+      <c r="W68">
         <v>3508</v>
       </c>
     </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>30</v>
       </c>
@@ -4711,59 +5545,71 @@
       <c r="C69" t="s">
         <v>28</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="1">
+        <f t="shared" si="3"/>
+        <v>486.80628272251312</v>
+      </c>
+      <c r="E69" s="1">
+        <f t="shared" si="4"/>
+        <v>293.71727748691097</v>
+      </c>
+      <c r="F69">
         <v>191</v>
       </c>
-      <c r="E69">
+      <c r="G69" s="1">
         <v>2.48</v>
       </c>
-      <c r="F69">
+      <c r="H69" s="1">
         <v>36.880000000000003</v>
       </c>
-      <c r="G69">
+      <c r="I69" s="1">
+        <f t="shared" si="5"/>
+        <v>34.291024000000007</v>
+      </c>
+      <c r="J69">
         <v>56.1</v>
       </c>
-      <c r="H69">
+      <c r="K69">
         <v>58.58</v>
       </c>
-      <c r="I69">
+      <c r="L69">
         <v>4354</v>
       </c>
-      <c r="J69">
+      <c r="M69">
         <v>4375</v>
       </c>
-      <c r="K69">
+      <c r="N69">
         <v>4373</v>
       </c>
-      <c r="L69">
+      <c r="O69">
         <v>62</v>
       </c>
-      <c r="M69">
+      <c r="P69">
         <v>64</v>
       </c>
-      <c r="N69">
+      <c r="Q69">
         <v>63</v>
       </c>
-      <c r="O69">
+      <c r="R69">
         <v>797</v>
       </c>
-      <c r="P69">
+      <c r="S69">
         <v>798</v>
       </c>
-      <c r="Q69">
+      <c r="T69">
         <v>798</v>
       </c>
-      <c r="R69">
+      <c r="U69">
         <v>3492</v>
       </c>
-      <c r="S69">
+      <c r="V69">
         <v>3514</v>
       </c>
-      <c r="T69">
+      <c r="W69">
         <v>3513</v>
       </c>
     </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>30</v>
       </c>
@@ -4773,59 +5619,71 @@
       <c r="C70" t="s">
         <v>28</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="1">
+        <f t="shared" si="3"/>
+        <v>433.27510917030565</v>
+      </c>
+      <c r="E70" s="1">
+        <f t="shared" si="4"/>
+        <v>265.41484716157203</v>
+      </c>
+      <c r="F70">
         <v>229</v>
       </c>
-      <c r="E70">
+      <c r="G70" s="1">
         <v>2.44</v>
       </c>
-      <c r="F70">
+      <c r="H70" s="1">
         <v>38.44</v>
       </c>
-      <c r="G70">
+      <c r="I70" s="1">
+        <f t="shared" si="5"/>
+        <v>38.140167999999996</v>
+      </c>
+      <c r="J70">
         <v>60.78</v>
       </c>
-      <c r="H70">
+      <c r="K70">
         <v>63.22</v>
       </c>
-      <c r="I70">
+      <c r="L70">
         <v>4378</v>
       </c>
-      <c r="J70">
+      <c r="M70">
         <v>4386</v>
       </c>
-      <c r="K70">
+      <c r="N70">
         <v>4380</v>
       </c>
-      <c r="L70">
+      <c r="O70">
         <v>63</v>
       </c>
-      <c r="M70">
+      <c r="P70">
         <v>67</v>
       </c>
-      <c r="N70">
+      <c r="Q70">
         <v>63</v>
       </c>
-      <c r="O70">
+      <c r="R70">
         <v>800</v>
       </c>
-      <c r="P70">
+      <c r="S70">
         <v>800</v>
       </c>
-      <c r="Q70">
+      <c r="T70">
         <v>800</v>
       </c>
-      <c r="R70">
+      <c r="U70">
         <v>3515</v>
       </c>
-      <c r="S70">
+      <c r="V70">
         <v>3519</v>
       </c>
-      <c r="T70">
+      <c r="W70">
         <v>3516</v>
       </c>
     </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>30</v>
       </c>
@@ -4835,59 +5693,71 @@
       <c r="C71" t="s">
         <v>28</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="1">
+        <f t="shared" si="3"/>
+        <v>829.01960784313724</v>
+      </c>
+      <c r="E71" s="1">
+        <f t="shared" si="4"/>
+        <v>464.31372549019608</v>
+      </c>
+      <c r="F71">
         <v>102</v>
       </c>
-      <c r="E71">
+      <c r="G71" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F71">
+      <c r="H71" s="1">
         <v>37.200000000000003</v>
       </c>
-      <c r="G71">
+      <c r="I71" s="1">
+        <f t="shared" si="5"/>
+        <v>31.456320000000002</v>
+      </c>
+      <c r="J71">
         <v>47.36</v>
       </c>
-      <c r="H71">
+      <c r="K71">
         <v>49.81</v>
       </c>
-      <c r="I71">
+      <c r="L71">
         <v>4382</v>
       </c>
-      <c r="J71">
+      <c r="M71">
         <v>4393</v>
       </c>
-      <c r="K71">
+      <c r="N71">
         <v>4385</v>
       </c>
-      <c r="L71">
+      <c r="O71">
         <v>63</v>
       </c>
-      <c r="M71">
+      <c r="P71">
         <v>68</v>
       </c>
-      <c r="N71">
+      <c r="Q71">
         <v>64</v>
       </c>
-      <c r="O71">
+      <c r="R71">
         <v>802</v>
       </c>
-      <c r="P71">
+      <c r="S71">
         <v>802</v>
       </c>
-      <c r="Q71">
+      <c r="T71">
         <v>802</v>
       </c>
-      <c r="R71">
+      <c r="U71">
         <v>3518</v>
       </c>
-      <c r="S71">
+      <c r="V71">
         <v>3523</v>
       </c>
-      <c r="T71">
+      <c r="W71">
         <v>3519</v>
       </c>
     </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>31</v>
       </c>
@@ -4897,59 +5767,71 @@
       <c r="C72" t="s">
         <v>28</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="1">
+        <f t="shared" si="3"/>
+        <v>2359</v>
+      </c>
+      <c r="E72" s="1">
+        <f t="shared" si="4"/>
+        <v>1246.75</v>
+      </c>
+      <c r="F72">
         <v>40</v>
       </c>
-      <c r="E72">
+      <c r="G72" s="1">
         <v>12.39</v>
       </c>
-      <c r="F72">
+      <c r="H72" s="1">
         <v>44.49</v>
       </c>
-      <c r="G72">
+      <c r="I72" s="1">
+        <f t="shared" si="5"/>
+        <v>41.980764000000001</v>
+      </c>
+      <c r="J72">
         <v>49.87</v>
       </c>
-      <c r="H72">
+      <c r="K72">
         <v>62.26</v>
       </c>
-      <c r="I72">
+      <c r="L72">
         <v>733</v>
       </c>
-      <c r="J72">
+      <c r="M72">
         <v>4542</v>
       </c>
-      <c r="K72">
+      <c r="N72">
         <v>3578</v>
       </c>
-      <c r="L72">
+      <c r="O72">
         <v>39</v>
       </c>
-      <c r="M72">
+      <c r="P72">
         <v>58</v>
       </c>
-      <c r="N72">
+      <c r="Q72">
         <v>51</v>
       </c>
-      <c r="O72">
+      <c r="R72">
         <v>632</v>
       </c>
-      <c r="P72">
+      <c r="S72">
         <v>787</v>
       </c>
-      <c r="Q72">
+      <c r="T72">
         <v>776</v>
       </c>
-      <c r="R72">
+      <c r="U72">
         <v>62</v>
       </c>
-      <c r="S72">
+      <c r="V72">
         <v>3696</v>
       </c>
-      <c r="T72">
+      <c r="W72">
         <v>2750</v>
       </c>
     </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>31</v>
       </c>
@@ -4959,59 +5841,71 @@
       <c r="C73" t="s">
         <v>28</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="1">
+        <f t="shared" si="3"/>
+        <v>1533.9999999999998</v>
+      </c>
+      <c r="E73" s="1">
+        <f t="shared" si="4"/>
+        <v>823.16666666666663</v>
+      </c>
+      <c r="F73">
         <v>60</v>
       </c>
-      <c r="E73">
+      <c r="G73" s="1">
         <v>2.71</v>
       </c>
-      <c r="F73">
+      <c r="H73" s="1">
         <v>42.65</v>
       </c>
-      <c r="G73">
+      <c r="I73" s="1">
+        <f t="shared" si="5"/>
+        <v>39.255059999999993</v>
+      </c>
+      <c r="J73">
         <v>49.39</v>
       </c>
-      <c r="H73">
+      <c r="K73">
         <v>52.1</v>
       </c>
-      <c r="I73">
+      <c r="L73">
         <v>4542</v>
       </c>
-      <c r="J73">
+      <c r="M73">
         <v>4550</v>
       </c>
-      <c r="K73">
+      <c r="N73">
         <v>4544</v>
       </c>
-      <c r="L73">
+      <c r="O73">
         <v>57</v>
       </c>
-      <c r="M73">
+      <c r="P73">
         <v>59</v>
       </c>
-      <c r="N73">
+      <c r="Q73">
         <v>57</v>
       </c>
-      <c r="O73">
+      <c r="R73">
         <v>789</v>
       </c>
-      <c r="P73">
+      <c r="S73">
         <v>789</v>
       </c>
-      <c r="Q73">
+      <c r="T73">
         <v>789</v>
       </c>
-      <c r="R73">
+      <c r="U73">
         <v>3696</v>
       </c>
-      <c r="S73">
+      <c r="V73">
         <v>3702</v>
       </c>
-      <c r="T73">
+      <c r="W73">
         <v>3698</v>
       </c>
     </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>31</v>
       </c>
@@ -5021,59 +5915,71 @@
       <c r="C74" t="s">
         <v>28</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="1">
+        <f t="shared" si="3"/>
+        <v>832.3</v>
+      </c>
+      <c r="E74" s="1">
+        <f t="shared" si="4"/>
+        <v>465.9</v>
+      </c>
+      <c r="F74">
         <v>100</v>
       </c>
-      <c r="E74">
+      <c r="G74" s="1">
         <v>2.82</v>
       </c>
-      <c r="F74">
+      <c r="H74" s="1">
         <v>36.64</v>
       </c>
-      <c r="G74">
+      <c r="I74" s="1">
+        <f t="shared" si="5"/>
+        <v>30.495472000000003</v>
+      </c>
+      <c r="J74">
         <v>46.59</v>
       </c>
-      <c r="H74">
+      <c r="K74">
         <v>49.41</v>
       </c>
-      <c r="I74">
+      <c r="L74">
         <v>4548</v>
       </c>
-      <c r="J74">
+      <c r="M74">
         <v>4556</v>
       </c>
-      <c r="K74">
+      <c r="N74">
         <v>4553</v>
       </c>
-      <c r="L74">
+      <c r="O74">
         <v>58</v>
       </c>
-      <c r="M74">
+      <c r="P74">
         <v>61</v>
       </c>
-      <c r="N74">
+      <c r="Q74">
         <v>60</v>
       </c>
-      <c r="O74">
+      <c r="R74">
         <v>791</v>
       </c>
-      <c r="P74">
+      <c r="S74">
         <v>791</v>
       </c>
-      <c r="Q74">
+      <c r="T74">
         <v>791</v>
       </c>
-      <c r="R74">
+      <c r="U74">
         <v>3700</v>
       </c>
-      <c r="S74">
+      <c r="V74">
         <v>3704</v>
       </c>
-      <c r="T74">
+      <c r="W74">
         <v>3702</v>
       </c>
     </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>31</v>
       </c>
@@ -5083,59 +5989,71 @@
       <c r="C75" t="s">
         <v>28</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="1">
+        <f t="shared" si="3"/>
+        <v>1250.8333333333335</v>
+      </c>
+      <c r="E75" s="1">
+        <f t="shared" si="4"/>
+        <v>674.16666666666663</v>
+      </c>
+      <c r="F75">
         <v>60</v>
       </c>
-      <c r="E75">
+      <c r="G75" s="1">
         <v>2.65</v>
       </c>
-      <c r="F75">
+      <c r="H75" s="1">
         <v>34.6</v>
       </c>
-      <c r="G75">
+      <c r="I75" s="1">
+        <f t="shared" si="5"/>
+        <v>25.967300000000005</v>
+      </c>
+      <c r="J75">
         <v>40.450000000000003</v>
       </c>
-      <c r="H75">
+      <c r="K75">
         <v>43.1</v>
       </c>
-      <c r="I75">
+      <c r="L75">
         <v>4557</v>
       </c>
-      <c r="J75">
+      <c r="M75">
         <v>4561</v>
       </c>
-      <c r="K75">
+      <c r="N75">
         <v>4558</v>
       </c>
-      <c r="L75">
+      <c r="O75">
         <v>60</v>
       </c>
-      <c r="M75">
+      <c r="P75">
         <v>61</v>
       </c>
-      <c r="N75">
+      <c r="Q75">
         <v>60</v>
       </c>
-      <c r="O75">
+      <c r="R75">
         <v>793</v>
       </c>
-      <c r="P75">
+      <c r="S75">
         <v>793</v>
       </c>
-      <c r="Q75">
+      <c r="T75">
         <v>793</v>
       </c>
-      <c r="R75">
+      <c r="U75">
         <v>3704</v>
       </c>
-      <c r="S75">
+      <c r="V75">
         <v>3708</v>
       </c>
-      <c r="T75">
+      <c r="W75">
         <v>3705</v>
       </c>
     </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>31</v>
       </c>
@@ -5145,59 +6063,71 @@
       <c r="C76" t="s">
         <v>28</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="1">
+        <f t="shared" si="3"/>
+        <v>2952.962962962963</v>
+      </c>
+      <c r="E76" s="1">
+        <f t="shared" si="4"/>
+        <v>1530</v>
+      </c>
+      <c r="F76">
         <v>27</v>
       </c>
-      <c r="E76">
+      <c r="G76" s="1">
         <v>2.74</v>
       </c>
-      <c r="F76">
+      <c r="H76" s="1">
         <v>38.42</v>
       </c>
-      <c r="G76">
+      <c r="I76" s="1">
+        <f t="shared" si="5"/>
+        <v>30.632266000000001</v>
+      </c>
+      <c r="J76">
         <v>41.31</v>
       </c>
-      <c r="H76">
+      <c r="K76">
         <v>44.05</v>
       </c>
-      <c r="I76">
+      <c r="L76">
         <v>4565</v>
       </c>
-      <c r="J76">
+      <c r="M76">
         <v>4574</v>
       </c>
-      <c r="K76">
+      <c r="N76">
         <v>4569</v>
       </c>
-      <c r="L76">
+      <c r="O76">
         <v>60</v>
       </c>
-      <c r="M76">
+      <c r="P76">
         <v>64</v>
       </c>
-      <c r="N76">
+      <c r="Q76">
         <v>62</v>
       </c>
-      <c r="O76">
+      <c r="R76">
         <v>796</v>
       </c>
-      <c r="P76">
+      <c r="S76">
         <v>797</v>
       </c>
-      <c r="Q76">
+      <c r="T76">
         <v>797</v>
       </c>
-      <c r="R76">
+      <c r="U76">
         <v>3708</v>
       </c>
-      <c r="S76">
+      <c r="V76">
         <v>3714</v>
       </c>
-      <c r="T76">
+      <c r="W76">
         <v>3710</v>
       </c>
     </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>31</v>
       </c>
@@ -5207,59 +6137,71 @@
       <c r="C77" t="s">
         <v>28</v>
       </c>
-      <c r="D77">
+      <c r="D77" s="1">
+        <f t="shared" si="3"/>
+        <v>570.40229885057477</v>
+      </c>
+      <c r="E77" s="1">
+        <f t="shared" si="4"/>
+        <v>339.31034482758622</v>
+      </c>
+      <c r="F77">
         <v>174</v>
       </c>
-      <c r="E77">
+      <c r="G77" s="1">
         <v>2.8</v>
       </c>
-      <c r="F77">
+      <c r="H77" s="1">
         <v>40.21</v>
       </c>
-      <c r="G77">
+      <c r="I77" s="1">
+        <f t="shared" si="5"/>
+        <v>39.908425000000001</v>
+      </c>
+      <c r="J77">
         <v>59.04</v>
       </c>
-      <c r="H77">
+      <c r="K77">
         <v>61.84</v>
       </c>
-      <c r="I77">
+      <c r="L77">
         <v>4566</v>
       </c>
-      <c r="J77">
+      <c r="M77">
         <v>4576</v>
       </c>
-      <c r="K77">
+      <c r="N77">
         <v>4568</v>
       </c>
-      <c r="L77">
+      <c r="O77">
         <v>59</v>
       </c>
-      <c r="M77">
+      <c r="P77">
         <v>63</v>
       </c>
-      <c r="N77">
+      <c r="Q77">
         <v>59</v>
       </c>
-      <c r="O77">
+      <c r="R77">
         <v>799</v>
       </c>
-      <c r="P77">
+      <c r="S77">
         <v>799</v>
       </c>
-      <c r="Q77">
+      <c r="T77">
         <v>799</v>
       </c>
-      <c r="R77">
+      <c r="U77">
         <v>3709</v>
       </c>
-      <c r="S77">
+      <c r="V77">
         <v>3714</v>
       </c>
-      <c r="T77">
+      <c r="W77">
         <v>3710</v>
       </c>
     </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>31</v>
       </c>
@@ -5269,59 +6211,71 @@
       <c r="C78" t="s">
         <v>28</v>
       </c>
-      <c r="D78">
+      <c r="D78" s="1">
+        <f t="shared" si="3"/>
+        <v>454.51754385964909</v>
+      </c>
+      <c r="E78" s="1">
+        <f t="shared" si="4"/>
+        <v>280.70175438596493</v>
+      </c>
+      <c r="F78">
         <v>228</v>
       </c>
-      <c r="E78">
+      <c r="G78" s="1">
         <v>2.67</v>
       </c>
-      <c r="F78">
+      <c r="H78" s="1">
         <v>39.630000000000003</v>
       </c>
-      <c r="G78">
+      <c r="I78" s="1">
+        <f t="shared" si="5"/>
+        <v>41.068569000000004</v>
+      </c>
+      <c r="J78">
         <v>64</v>
       </c>
-      <c r="H78">
+      <c r="K78">
         <v>66.67</v>
       </c>
-      <c r="I78">
+      <c r="L78">
         <v>4572</v>
       </c>
-      <c r="J78">
+      <c r="M78">
         <v>4580</v>
       </c>
-      <c r="K78">
+      <c r="N78">
         <v>4574</v>
       </c>
-      <c r="L78">
+      <c r="O78">
         <v>59</v>
       </c>
-      <c r="M78">
+      <c r="P78">
         <v>63</v>
       </c>
-      <c r="N78">
+      <c r="Q78">
         <v>60</v>
       </c>
-      <c r="O78">
+      <c r="R78">
         <v>801</v>
       </c>
-      <c r="P78">
+      <c r="S78">
         <v>801</v>
       </c>
-      <c r="Q78">
+      <c r="T78">
         <v>801</v>
       </c>
-      <c r="R78">
+      <c r="U78">
         <v>3712</v>
       </c>
-      <c r="S78">
+      <c r="V78">
         <v>3716</v>
       </c>
-      <c r="T78">
+      <c r="W78">
         <v>3713</v>
       </c>
     </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>31</v>
       </c>
@@ -5331,59 +6285,71 @@
       <c r="C79" t="s">
         <v>28</v>
       </c>
-      <c r="D79">
+      <c r="D79" s="1">
+        <f t="shared" si="3"/>
+        <v>4262.6315789473692</v>
+      </c>
+      <c r="E79" s="1">
+        <f t="shared" si="4"/>
+        <v>2183.6842105263158</v>
+      </c>
+      <c r="F79">
         <v>19</v>
       </c>
-      <c r="E79">
+      <c r="G79" s="1">
         <v>2.74</v>
       </c>
-      <c r="F79">
+      <c r="H79" s="1">
         <v>39.5</v>
       </c>
-      <c r="G79">
+      <c r="I79" s="1">
+        <f t="shared" si="5"/>
+        <v>31.991050000000001</v>
+      </c>
+      <c r="J79">
         <v>41.49</v>
       </c>
-      <c r="H79">
+      <c r="K79">
         <v>44.23</v>
       </c>
-      <c r="I79">
+      <c r="L79">
         <v>4576</v>
       </c>
-      <c r="J79">
+      <c r="M79">
         <v>4586</v>
       </c>
-      <c r="K79">
+      <c r="N79">
         <v>4577</v>
       </c>
-      <c r="L79">
+      <c r="O79">
         <v>60</v>
       </c>
-      <c r="M79">
+      <c r="P79">
         <v>65</v>
       </c>
-      <c r="N79">
+      <c r="Q79">
         <v>61</v>
       </c>
-      <c r="O79">
+      <c r="R79">
         <v>803</v>
       </c>
-      <c r="P79">
+      <c r="S79">
         <v>803</v>
       </c>
-      <c r="Q79">
+      <c r="T79">
         <v>803</v>
       </c>
-      <c r="R79">
+      <c r="U79">
         <v>3713</v>
       </c>
-      <c r="S79">
+      <c r="V79">
         <v>3718</v>
       </c>
-      <c r="T79">
+      <c r="W79">
         <v>3714</v>
       </c>
     </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>32</v>
       </c>
@@ -5393,59 +6359,71 @@
       <c r="C80" t="s">
         <v>28</v>
       </c>
-      <c r="D80">
+      <c r="D80" s="1">
+        <f t="shared" si="3"/>
+        <v>2246</v>
+      </c>
+      <c r="E80" s="1">
+        <f t="shared" si="4"/>
+        <v>1174.25</v>
+      </c>
+      <c r="F80">
         <v>40</v>
       </c>
-      <c r="E80">
+      <c r="G80" s="1">
         <v>6.99</v>
       </c>
-      <c r="F80">
+      <c r="H80" s="1">
         <v>42.87</v>
       </c>
-      <c r="G80">
+      <c r="I80" s="1">
+        <f t="shared" si="5"/>
+        <v>38.514408000000003</v>
+      </c>
+      <c r="J80">
         <v>46.97</v>
       </c>
-      <c r="H80">
+      <c r="K80">
         <v>53.96</v>
       </c>
-      <c r="I80">
+      <c r="L80">
         <v>733</v>
       </c>
-      <c r="J80">
+      <c r="M80">
         <v>4548</v>
       </c>
-      <c r="K80">
+      <c r="N80">
         <v>3817</v>
       </c>
-      <c r="L80">
+      <c r="O80">
         <v>39</v>
       </c>
-      <c r="M80">
+      <c r="P80">
         <v>57</v>
       </c>
-      <c r="N80">
+      <c r="Q80">
         <v>51</v>
       </c>
-      <c r="O80">
+      <c r="R80">
         <v>634</v>
       </c>
-      <c r="P80">
+      <c r="S80">
         <v>786</v>
       </c>
-      <c r="Q80">
+      <c r="T80">
         <v>780</v>
       </c>
-      <c r="R80">
+      <c r="U80">
         <v>59</v>
       </c>
-      <c r="S80">
+      <c r="V80">
         <v>3705</v>
       </c>
-      <c r="T80">
+      <c r="W80">
         <v>2985</v>
       </c>
     </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>32</v>
       </c>
@@ -5455,59 +6433,71 @@
       <c r="C81" t="s">
         <v>28</v>
       </c>
-      <c r="D81">
+      <c r="D81" s="1">
+        <f t="shared" si="3"/>
+        <v>1835.5319148936171</v>
+      </c>
+      <c r="E81" s="1">
+        <f t="shared" si="4"/>
+        <v>968.936170212766</v>
+      </c>
+      <c r="F81">
         <v>47</v>
       </c>
-      <c r="E81">
+      <c r="G81" s="1">
         <v>2.48</v>
       </c>
-      <c r="F81">
+      <c r="H81" s="1">
         <v>40.729999999999997</v>
       </c>
-      <c r="G81">
+      <c r="I81" s="1">
+        <f t="shared" si="5"/>
+        <v>35.137770999999994</v>
+      </c>
+      <c r="J81">
         <v>45.54</v>
       </c>
-      <c r="H81">
+      <c r="K81">
         <v>48.02</v>
       </c>
-      <c r="I81">
+      <c r="L81">
         <v>4550</v>
       </c>
-      <c r="J81">
+      <c r="M81">
         <v>4557</v>
       </c>
-      <c r="K81">
+      <c r="N81">
         <v>4551</v>
       </c>
-      <c r="L81">
+      <c r="O81">
         <v>56</v>
       </c>
-      <c r="M81">
+      <c r="P81">
         <v>59</v>
       </c>
-      <c r="N81">
+      <c r="Q81">
         <v>57</v>
       </c>
-      <c r="O81">
+      <c r="R81">
         <v>788</v>
       </c>
-      <c r="P81">
+      <c r="S81">
         <v>788</v>
       </c>
-      <c r="Q81">
+      <c r="T81">
         <v>788</v>
       </c>
-      <c r="R81">
+      <c r="U81">
         <v>3704</v>
       </c>
-      <c r="S81">
+      <c r="V81">
         <v>3710</v>
       </c>
-      <c r="T81">
+      <c r="W81">
         <v>3706</v>
       </c>
     </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>32</v>
       </c>
@@ -5517,59 +6507,71 @@
       <c r="C82" t="s">
         <v>28</v>
       </c>
-      <c r="D82">
+      <c r="D82" s="1">
+        <f t="shared" si="3"/>
+        <v>920.3125</v>
+      </c>
+      <c r="E82" s="1">
+        <f t="shared" si="4"/>
+        <v>513.02083333333337</v>
+      </c>
+      <c r="F82">
         <v>96</v>
       </c>
-      <c r="E82">
+      <c r="G82" s="1">
         <v>2.5</v>
       </c>
-      <c r="F82">
+      <c r="H82" s="1">
         <v>39.1</v>
       </c>
-      <c r="G82">
+      <c r="I82" s="1">
+        <f t="shared" si="5"/>
+        <v>34.544849999999997</v>
+      </c>
+      <c r="J82">
         <v>49.25</v>
       </c>
-      <c r="H82">
+      <c r="K82">
         <v>51.74</v>
       </c>
-      <c r="I82">
+      <c r="L82">
         <v>4554</v>
       </c>
-      <c r="J82">
+      <c r="M82">
         <v>4557</v>
       </c>
-      <c r="K82">
+      <c r="N82">
         <v>4555</v>
       </c>
-      <c r="L82">
+      <c r="O82">
         <v>57</v>
       </c>
-      <c r="M82">
+      <c r="P82">
         <v>58</v>
       </c>
-      <c r="N82">
+      <c r="Q82">
         <v>58</v>
       </c>
-      <c r="O82">
+      <c r="R82">
         <v>789</v>
       </c>
-      <c r="P82">
+      <c r="S82">
         <v>789</v>
       </c>
-      <c r="Q82">
+      <c r="T82">
         <v>789</v>
       </c>
-      <c r="R82">
+      <c r="U82">
         <v>3708</v>
       </c>
-      <c r="S82">
+      <c r="V82">
         <v>3710</v>
       </c>
-      <c r="T82">
+      <c r="W82">
         <v>3708</v>
       </c>
     </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>32</v>
       </c>
@@ -5579,59 +6581,71 @@
       <c r="C83" t="s">
         <v>28</v>
       </c>
-      <c r="D83">
+      <c r="D83" s="1">
+        <f t="shared" si="3"/>
+        <v>4002.6315789473692</v>
+      </c>
+      <c r="E83" s="1">
+        <f t="shared" si="4"/>
+        <v>2053.6842105263158</v>
+      </c>
+      <c r="F83">
         <v>19</v>
       </c>
-      <c r="E83">
+      <c r="G83" s="1">
         <v>2.4300000000000002</v>
       </c>
-      <c r="F83">
+      <c r="H83" s="1">
         <v>37.03</v>
       </c>
-      <c r="G83">
+      <c r="I83" s="1">
+        <f t="shared" si="5"/>
+        <v>28.161315000000002</v>
+      </c>
+      <c r="J83">
         <v>39.020000000000003</v>
       </c>
-      <c r="H83">
+      <c r="K83">
         <v>41.45</v>
       </c>
-      <c r="I83">
+      <c r="L83">
         <v>4559</v>
       </c>
-      <c r="J83">
+      <c r="M83">
         <v>4561</v>
       </c>
-      <c r="K83">
+      <c r="N83">
         <v>4560</v>
       </c>
-      <c r="L83">
+      <c r="O83">
         <v>57</v>
       </c>
-      <c r="M83">
+      <c r="P83">
         <v>58</v>
       </c>
-      <c r="N83">
+      <c r="Q83">
         <v>58</v>
       </c>
-      <c r="O83">
+      <c r="R83">
         <v>792</v>
       </c>
-      <c r="P83">
+      <c r="S83">
         <v>792</v>
       </c>
-      <c r="Q83">
+      <c r="T83">
         <v>792</v>
       </c>
-      <c r="R83">
+      <c r="U83">
         <v>3710</v>
       </c>
-      <c r="S83">
+      <c r="V83">
         <v>3712</v>
       </c>
-      <c r="T83">
+      <c r="W83">
         <v>3710</v>
       </c>
     </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>32</v>
       </c>
@@ -5641,59 +6655,71 @@
       <c r="C84" t="s">
         <v>28</v>
       </c>
-      <c r="D84">
+      <c r="D84" s="1">
+        <f t="shared" si="3"/>
+        <v>2438.787878787879</v>
+      </c>
+      <c r="E84" s="1">
+        <f t="shared" si="4"/>
+        <v>1271.5151515151515</v>
+      </c>
+      <c r="F84">
         <v>33</v>
       </c>
-      <c r="E84">
+      <c r="G84" s="1">
         <v>2.42</v>
       </c>
-      <c r="F84">
+      <c r="H84" s="1">
         <v>38.520000000000003</v>
       </c>
-      <c r="G84">
+      <c r="I84" s="1">
+        <f t="shared" si="5"/>
+        <v>31.000896000000004</v>
+      </c>
+      <c r="J84">
         <v>41.96</v>
       </c>
-      <c r="H84">
+      <c r="K84">
         <v>44.39</v>
       </c>
-      <c r="I84">
+      <c r="L84">
         <v>4565</v>
       </c>
-      <c r="J84">
+      <c r="M84">
         <v>4571</v>
       </c>
-      <c r="K84">
+      <c r="N84">
         <v>4567</v>
       </c>
-      <c r="L84">
+      <c r="O84">
         <v>58</v>
       </c>
-      <c r="M84">
+      <c r="P84">
         <v>60</v>
       </c>
-      <c r="N84">
+      <c r="Q84">
         <v>58</v>
       </c>
-      <c r="O84">
+      <c r="R84">
         <v>795</v>
       </c>
-      <c r="P84">
+      <c r="S84">
         <v>795</v>
       </c>
-      <c r="Q84">
+      <c r="T84">
         <v>795</v>
       </c>
-      <c r="R84">
+      <c r="U84">
         <v>3712</v>
       </c>
-      <c r="S84">
+      <c r="V84">
         <v>3716</v>
       </c>
-      <c r="T84">
+      <c r="W84">
         <v>3713</v>
       </c>
     </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>32</v>
       </c>
@@ -5703,59 +6729,71 @@
       <c r="C85" t="s">
         <v>28</v>
       </c>
-      <c r="D85">
+      <c r="D85" s="1">
+        <f t="shared" si="3"/>
+        <v>918.84210526315792</v>
+      </c>
+      <c r="E85" s="1">
+        <f t="shared" si="4"/>
+        <v>511.4736842105263</v>
+      </c>
+      <c r="F85">
         <v>95</v>
       </c>
-      <c r="E85">
+      <c r="G85" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F85">
+      <c r="H85" s="1">
         <v>38.700000000000003</v>
       </c>
-      <c r="G85">
+      <c r="I85" s="1">
+        <f t="shared" si="5"/>
+        <v>33.781230000000001</v>
+      </c>
+      <c r="J85">
         <v>48.59</v>
       </c>
-      <c r="H85">
+      <c r="K85">
         <v>51.06</v>
       </c>
-      <c r="I85">
+      <c r="L85">
         <v>4571</v>
       </c>
-      <c r="J85">
+      <c r="M85">
         <v>4574</v>
       </c>
-      <c r="K85">
+      <c r="N85">
         <v>4572</v>
       </c>
-      <c r="L85">
+      <c r="O85">
         <v>58</v>
       </c>
-      <c r="M85">
+      <c r="P85">
         <v>59</v>
       </c>
-      <c r="N85">
+      <c r="Q85">
         <v>59</v>
       </c>
-      <c r="O85">
+      <c r="R85">
         <v>797</v>
       </c>
-      <c r="P85">
+      <c r="S85">
         <v>797</v>
       </c>
-      <c r="Q85">
+      <c r="T85">
         <v>797</v>
       </c>
-      <c r="R85">
+      <c r="U85">
         <v>3715</v>
       </c>
-      <c r="S85">
+      <c r="V85">
         <v>3717</v>
       </c>
-      <c r="T85">
+      <c r="W85">
         <v>3716</v>
       </c>
     </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>32</v>
       </c>
@@ -5765,59 +6803,71 @@
       <c r="C86" t="s">
         <v>28</v>
       </c>
-      <c r="D86">
+      <c r="D86" s="1">
+        <f t="shared" si="3"/>
+        <v>339.51367781155011</v>
+      </c>
+      <c r="E86" s="1">
+        <f t="shared" si="4"/>
+        <v>222.79635258358664</v>
+      </c>
+      <c r="F86">
         <v>329</v>
       </c>
-      <c r="E86">
+      <c r="G86" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F86">
+      <c r="H86" s="1">
         <v>38.4</v>
       </c>
-      <c r="G86">
+      <c r="I86" s="1">
+        <f t="shared" si="5"/>
+        <v>42.892800000000001</v>
+      </c>
+      <c r="J86">
         <v>73.3</v>
       </c>
-      <c r="H86">
+      <c r="K86">
         <v>75.77</v>
       </c>
-      <c r="I86">
+      <c r="L86">
         <v>4577</v>
       </c>
-      <c r="J86">
+      <c r="M86">
         <v>4585</v>
       </c>
-      <c r="K86">
+      <c r="N86">
         <v>4579</v>
       </c>
-      <c r="L86">
+      <c r="O86">
         <v>59</v>
       </c>
-      <c r="M86">
+      <c r="P86">
         <v>63</v>
       </c>
-      <c r="N86">
+      <c r="Q86">
         <v>59</v>
       </c>
-      <c r="O86">
+      <c r="R86">
         <v>799</v>
       </c>
-      <c r="P86">
+      <c r="S86">
         <v>800</v>
       </c>
-      <c r="Q86">
+      <c r="T86">
         <v>800</v>
       </c>
-      <c r="R86">
+      <c r="U86">
         <v>3718</v>
       </c>
-      <c r="S86">
+      <c r="V86">
         <v>3722</v>
       </c>
-      <c r="T86">
+      <c r="W86">
         <v>3719</v>
       </c>
     </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>32</v>
       </c>
@@ -5827,59 +6877,71 @@
       <c r="C87" t="s">
         <v>28</v>
       </c>
-      <c r="D87">
+      <c r="D87" s="1">
+        <f t="shared" si="3"/>
+        <v>2802.0689655172414</v>
+      </c>
+      <c r="E87" s="1">
+        <f t="shared" si="4"/>
+        <v>1452.7586206896551</v>
+      </c>
+      <c r="F87">
         <v>29</v>
       </c>
-      <c r="E87">
+      <c r="G87" s="1">
         <v>2.4300000000000002</v>
       </c>
-      <c r="F87">
+      <c r="H87" s="1">
         <v>39.130000000000003</v>
       </c>
-      <c r="G87">
+      <c r="I87" s="1">
+        <f t="shared" si="5"/>
+        <v>31.797038000000008</v>
+      </c>
+      <c r="J87">
         <v>42.13</v>
       </c>
-      <c r="H87">
+      <c r="K87">
         <v>44.56</v>
       </c>
-      <c r="I87">
+      <c r="L87">
         <v>4581</v>
       </c>
-      <c r="J87">
+      <c r="M87">
         <v>4592</v>
       </c>
-      <c r="K87">
+      <c r="N87">
         <v>4582</v>
       </c>
-      <c r="L87">
+      <c r="O87">
         <v>59</v>
       </c>
-      <c r="M87">
+      <c r="P87">
         <v>64</v>
       </c>
-      <c r="N87">
+      <c r="Q87">
         <v>60</v>
       </c>
-      <c r="O87">
+      <c r="R87">
         <v>802</v>
       </c>
-      <c r="P87">
+      <c r="S87">
         <v>802</v>
       </c>
-      <c r="Q87">
+      <c r="T87">
         <v>802</v>
       </c>
-      <c r="R87">
+      <c r="U87">
         <v>3720</v>
       </c>
-      <c r="S87">
+      <c r="V87">
         <v>3725</v>
       </c>
-      <c r="T87">
+      <c r="W87">
         <v>3720</v>
       </c>
     </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>33</v>
       </c>
@@ -5889,59 +6951,71 @@
       <c r="C88" t="s">
         <v>28</v>
       </c>
-      <c r="D88">
+      <c r="D88" s="1">
+        <f t="shared" si="3"/>
+        <v>1268.6363636363635</v>
+      </c>
+      <c r="E88" s="1">
+        <f t="shared" si="4"/>
+        <v>683.030303030303</v>
+      </c>
+      <c r="F88">
         <v>66</v>
       </c>
-      <c r="E88">
+      <c r="G88" s="1">
         <v>6.47</v>
       </c>
-      <c r="F88">
+      <c r="H88" s="1">
         <v>38.65</v>
       </c>
-      <c r="G88">
+      <c r="I88" s="1">
+        <f t="shared" si="5"/>
+        <v>32.361644999999996</v>
+      </c>
+      <c r="J88">
         <v>45.08</v>
       </c>
-      <c r="H88">
+      <c r="K88">
         <v>51.55</v>
       </c>
-      <c r="I88">
+      <c r="L88">
         <v>731</v>
       </c>
-      <c r="J88">
+      <c r="M88">
         <v>4264</v>
       </c>
-      <c r="K88">
+      <c r="N88">
         <v>3650</v>
       </c>
-      <c r="L88">
+      <c r="O88">
         <v>39</v>
       </c>
-      <c r="M88">
+      <c r="P88">
         <v>57</v>
       </c>
-      <c r="N88">
+      <c r="Q88">
         <v>52</v>
       </c>
-      <c r="O88">
+      <c r="R88">
         <v>632</v>
       </c>
-      <c r="P88">
+      <c r="S88">
         <v>787</v>
       </c>
-      <c r="Q88">
+      <c r="T88">
         <v>781</v>
       </c>
-      <c r="R88">
+      <c r="U88">
         <v>59</v>
       </c>
-      <c r="S88">
+      <c r="V88">
         <v>3420</v>
       </c>
-      <c r="T88">
+      <c r="W88">
         <v>2817</v>
       </c>
     </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>33</v>
       </c>
@@ -5951,59 +7025,71 @@
       <c r="C89" t="s">
         <v>28</v>
       </c>
-      <c r="D89">
+      <c r="D89" s="1">
+        <f t="shared" si="3"/>
+        <v>1395.9649122807018</v>
+      </c>
+      <c r="E89" s="1">
+        <f t="shared" si="4"/>
+        <v>747.19298245614038</v>
+      </c>
+      <c r="F89">
         <v>57</v>
       </c>
-      <c r="E89">
+      <c r="G89" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F89">
+      <c r="H89" s="1">
         <v>36.979999999999997</v>
       </c>
-      <c r="G89">
+      <c r="I89" s="1">
+        <f t="shared" si="5"/>
+        <v>29.424985999999997</v>
+      </c>
+      <c r="J89">
         <v>42.59</v>
       </c>
-      <c r="H89">
+      <c r="K89">
         <v>45.06</v>
       </c>
-      <c r="I89">
+      <c r="L89">
         <v>4265</v>
       </c>
-      <c r="J89">
+      <c r="M89">
         <v>4272</v>
       </c>
-      <c r="K89">
+      <c r="N89">
         <v>4270</v>
       </c>
-      <c r="L89">
+      <c r="O89">
         <v>57</v>
       </c>
-      <c r="M89">
+      <c r="P89">
         <v>58</v>
       </c>
-      <c r="N89">
+      <c r="Q89">
         <v>57</v>
       </c>
-      <c r="O89">
+      <c r="R89">
         <v>788</v>
       </c>
-      <c r="P89">
+      <c r="S89">
         <v>788</v>
       </c>
-      <c r="Q89">
+      <c r="T89">
         <v>788</v>
       </c>
-      <c r="R89">
+      <c r="U89">
         <v>3419</v>
       </c>
-      <c r="S89">
+      <c r="V89">
         <v>3426</v>
       </c>
-      <c r="T89">
+      <c r="W89">
         <v>3424</v>
       </c>
     </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>33</v>
       </c>
@@ -6013,59 +7099,71 @@
       <c r="C90" t="s">
         <v>28</v>
       </c>
-      <c r="D90">
+      <c r="D90" s="1">
+        <f t="shared" si="3"/>
+        <v>999.48717948717967</v>
+      </c>
+      <c r="E90" s="1">
+        <f t="shared" si="4"/>
+        <v>548.97435897435901</v>
+      </c>
+      <c r="F90">
         <v>78</v>
       </c>
-      <c r="E90">
+      <c r="G90" s="1">
         <v>2.5</v>
       </c>
-      <c r="F90">
+      <c r="H90" s="1">
         <v>35.14</v>
       </c>
-      <c r="G90">
+      <c r="I90" s="1">
+        <f t="shared" si="5"/>
+        <v>27.395144000000002</v>
+      </c>
+      <c r="J90">
         <v>42.82</v>
       </c>
-      <c r="H90">
+      <c r="K90">
         <v>45.32</v>
       </c>
-      <c r="I90">
+      <c r="L90">
         <v>4274</v>
       </c>
-      <c r="J90">
+      <c r="M90">
         <v>4277</v>
       </c>
-      <c r="K90">
+      <c r="N90">
         <v>4275</v>
       </c>
-      <c r="L90">
+      <c r="O90">
         <v>57</v>
       </c>
-      <c r="M90">
+      <c r="P90">
         <v>59</v>
       </c>
-      <c r="N90">
+      <c r="Q90">
         <v>58</v>
       </c>
-      <c r="O90">
+      <c r="R90">
         <v>790</v>
       </c>
-      <c r="P90">
+      <c r="S90">
         <v>790</v>
       </c>
-      <c r="Q90">
+      <c r="T90">
         <v>790</v>
       </c>
-      <c r="R90">
+      <c r="U90">
         <v>3427</v>
       </c>
-      <c r="S90">
+      <c r="V90">
         <v>3429</v>
       </c>
-      <c r="T90">
+      <c r="W90">
         <v>3427</v>
       </c>
     </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>33</v>
       </c>
@@ -6075,59 +7173,71 @@
       <c r="C91" t="s">
         <v>28</v>
       </c>
-      <c r="D91">
+      <c r="D91" s="1">
+        <f t="shared" si="3"/>
+        <v>1141.5</v>
+      </c>
+      <c r="E91" s="1">
+        <f t="shared" si="4"/>
+        <v>619.16666666666663</v>
+      </c>
+      <c r="F91">
         <v>60</v>
       </c>
-      <c r="E91">
+      <c r="G91" s="1">
         <v>2.4500000000000002</v>
       </c>
-      <c r="F91">
+      <c r="H91" s="1">
         <v>31.34</v>
       </c>
-      <c r="G91">
+      <c r="I91" s="1">
+        <f t="shared" si="5"/>
+        <v>21.464765999999997</v>
+      </c>
+      <c r="J91">
         <v>37.15</v>
       </c>
-      <c r="H91">
+      <c r="K91">
         <v>39.6</v>
       </c>
-      <c r="I91">
+      <c r="L91">
         <v>4279</v>
       </c>
-      <c r="J91">
+      <c r="M91">
         <v>4282</v>
       </c>
-      <c r="K91">
+      <c r="N91">
         <v>4280</v>
       </c>
-      <c r="L91">
+      <c r="O91">
         <v>57</v>
       </c>
-      <c r="M91">
+      <c r="P91">
         <v>58</v>
       </c>
-      <c r="N91">
+      <c r="Q91">
         <v>58</v>
       </c>
-      <c r="O91">
+      <c r="R91">
         <v>793</v>
       </c>
-      <c r="P91">
+      <c r="S91">
         <v>793</v>
       </c>
-      <c r="Q91">
+      <c r="T91">
         <v>793</v>
       </c>
-      <c r="R91">
+      <c r="U91">
         <v>3429</v>
       </c>
-      <c r="S91">
+      <c r="V91">
         <v>3431</v>
       </c>
-      <c r="T91">
+      <c r="W91">
         <v>3430</v>
       </c>
     </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>33</v>
       </c>
@@ -6137,59 +7247,71 @@
       <c r="C92" t="s">
         <v>28</v>
       </c>
-      <c r="D92">
+      <c r="D92" s="1">
+        <f t="shared" si="3"/>
+        <v>2114.2857142857142</v>
+      </c>
+      <c r="E92" s="1">
+        <f t="shared" si="4"/>
+        <v>1106.5714285714287</v>
+      </c>
+      <c r="F92">
         <v>35</v>
       </c>
-      <c r="E92">
+      <c r="G92" s="1">
         <v>2.44</v>
       </c>
-      <c r="F92">
+      <c r="H92" s="1">
         <v>35.270000000000003</v>
       </c>
-      <c r="G92">
+      <c r="I92" s="1">
+        <f t="shared" si="5"/>
+        <v>26.099800000000002</v>
+      </c>
+      <c r="J92">
         <v>38.729999999999997</v>
       </c>
-      <c r="H92">
+      <c r="K92">
         <v>41.17</v>
       </c>
-      <c r="I92">
+      <c r="L92">
         <v>4285</v>
       </c>
-      <c r="J92">
+      <c r="M92">
         <v>4290</v>
       </c>
-      <c r="K92">
+      <c r="N92">
         <v>4286</v>
       </c>
-      <c r="L92">
+      <c r="O92">
         <v>58</v>
       </c>
-      <c r="M92">
+      <c r="P92">
         <v>59</v>
       </c>
-      <c r="N92">
+      <c r="Q92">
         <v>58</v>
       </c>
-      <c r="O92">
+      <c r="R92">
         <v>795</v>
       </c>
-      <c r="P92">
+      <c r="S92">
         <v>796</v>
       </c>
-      <c r="Q92">
+      <c r="T92">
         <v>796</v>
       </c>
-      <c r="R92">
+      <c r="U92">
         <v>3432</v>
       </c>
-      <c r="S92">
+      <c r="V92">
         <v>3436</v>
       </c>
-      <c r="T92">
+      <c r="W92">
         <v>3433</v>
       </c>
     </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>33</v>
       </c>
@@ -6199,59 +7321,71 @@
       <c r="C93" t="s">
         <v>28</v>
       </c>
-      <c r="D93">
+      <c r="D93" s="1">
+        <f t="shared" si="3"/>
+        <v>569.74358974358972</v>
+      </c>
+      <c r="E93" s="1">
+        <f t="shared" si="4"/>
+        <v>334.4871794871795</v>
+      </c>
+      <c r="F93">
         <v>156</v>
       </c>
-      <c r="E93">
+      <c r="G93" s="1">
         <v>2.46</v>
       </c>
-      <c r="F93">
+      <c r="H93" s="1">
         <v>36.700000000000003</v>
       </c>
-      <c r="G93">
+      <c r="I93" s="1">
+        <f t="shared" si="5"/>
+        <v>32.618960000000001</v>
+      </c>
+      <c r="J93">
         <v>52.18</v>
       </c>
-      <c r="H93">
+      <c r="K93">
         <v>54.64</v>
       </c>
-      <c r="I93">
+      <c r="L93">
         <v>4291</v>
       </c>
-      <c r="J93">
+      <c r="M93">
         <v>4295</v>
       </c>
-      <c r="K93">
+      <c r="N93">
         <v>4293</v>
       </c>
-      <c r="L93">
+      <c r="O93">
         <v>58</v>
       </c>
-      <c r="M93">
+      <c r="P93">
         <v>59</v>
       </c>
-      <c r="N93">
+      <c r="Q93">
         <v>58</v>
       </c>
-      <c r="O93">
+      <c r="R93">
         <v>798</v>
       </c>
-      <c r="P93">
+      <c r="S93">
         <v>798</v>
       </c>
-      <c r="Q93">
+      <c r="T93">
         <v>798</v>
       </c>
-      <c r="R93">
+      <c r="U93">
         <v>3435</v>
       </c>
-      <c r="S93">
+      <c r="V93">
         <v>3438</v>
       </c>
-      <c r="T93">
+      <c r="W93">
         <v>3436</v>
       </c>
     </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>33</v>
       </c>
@@ -6261,59 +7395,71 @@
       <c r="C94" t="s">
         <v>28</v>
       </c>
-      <c r="D94">
+      <c r="D94" s="1">
+        <f t="shared" si="3"/>
+        <v>400.33898305084745</v>
+      </c>
+      <c r="E94" s="1">
+        <f t="shared" si="4"/>
+        <v>249.95762711864407</v>
+      </c>
+      <c r="F94">
         <v>236</v>
       </c>
-      <c r="E94">
+      <c r="G94" s="1">
         <v>2.89</v>
       </c>
-      <c r="F94">
+      <c r="H94" s="1">
         <v>35.49</v>
       </c>
-      <c r="G94">
+      <c r="I94" s="1">
+        <f t="shared" si="5"/>
+        <v>33.530952000000006</v>
+      </c>
+      <c r="J94">
         <v>58.99</v>
       </c>
-      <c r="H94">
+      <c r="K94">
         <v>61.88</v>
       </c>
-      <c r="I94">
+      <c r="L94">
         <v>4298</v>
       </c>
-      <c r="J94">
+      <c r="M94">
         <v>4306</v>
       </c>
-      <c r="K94">
+      <c r="N94">
         <v>4301</v>
       </c>
-      <c r="L94">
+      <c r="O94">
         <v>59</v>
       </c>
-      <c r="M94">
+      <c r="P94">
         <v>63</v>
       </c>
-      <c r="N94">
+      <c r="Q94">
         <v>60</v>
       </c>
-      <c r="O94">
+      <c r="R94">
         <v>799</v>
       </c>
-      <c r="P94">
+      <c r="S94">
         <v>800</v>
       </c>
-      <c r="Q94">
+      <c r="T94">
         <v>800</v>
       </c>
-      <c r="R94">
+      <c r="U94">
         <v>3439</v>
       </c>
-      <c r="S94">
+      <c r="V94">
         <v>3444</v>
       </c>
-      <c r="T94">
+      <c r="W94">
         <v>3441</v>
       </c>
     </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>33</v>
       </c>
@@ -6323,59 +7469,71 @@
       <c r="C95" t="s">
         <v>28</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="1">
+        <f t="shared" si="3"/>
+        <v>1313.3333333333335</v>
+      </c>
+      <c r="E95" s="1">
+        <f t="shared" si="4"/>
+        <v>706.33333333333337</v>
+      </c>
+      <c r="F95">
         <v>60</v>
       </c>
-      <c r="E95">
+      <c r="G95" s="1">
         <v>2.4300000000000002</v>
       </c>
-      <c r="F95">
+      <c r="H95" s="1">
         <v>36.42</v>
       </c>
-      <c r="G95">
+      <c r="I95" s="1">
+        <f t="shared" si="5"/>
+        <v>28.698960000000007</v>
+      </c>
+      <c r="J95">
         <v>42.38</v>
       </c>
-      <c r="H95">
+      <c r="K95">
         <v>44.8</v>
       </c>
-      <c r="I95">
+      <c r="L95">
         <v>4307</v>
       </c>
-      <c r="J95">
+      <c r="M95">
         <v>4318</v>
       </c>
-      <c r="K95">
+      <c r="N95">
         <v>4309</v>
       </c>
-      <c r="L95">
+      <c r="O95">
         <v>61</v>
       </c>
-      <c r="M95">
+      <c r="P95">
         <v>66</v>
       </c>
-      <c r="N95">
+      <c r="Q95">
         <v>62</v>
       </c>
-      <c r="O95">
+      <c r="R95">
         <v>802</v>
       </c>
-      <c r="P95">
+      <c r="S95">
         <v>802</v>
       </c>
-      <c r="Q95">
+      <c r="T95">
         <v>802</v>
       </c>
-      <c r="R95">
+      <c r="U95">
         <v>3444</v>
       </c>
-      <c r="S95">
+      <c r="V95">
         <v>3450</v>
       </c>
-      <c r="T95">
+      <c r="W95">
         <v>3445</v>
       </c>
     </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>33</v>
       </c>
@@ -6385,55 +7543,67 @@
       <c r="C96" t="s">
         <v>28</v>
       </c>
-      <c r="D96">
+      <c r="D96" s="1">
+        <f t="shared" si="3"/>
+        <v>89.666666666666671</v>
+      </c>
+      <c r="E96" s="1">
+        <f t="shared" si="4"/>
+        <v>86</v>
+      </c>
+      <c r="F96">
         <v>30</v>
       </c>
-      <c r="E96">
+      <c r="G96" s="1">
         <v>2.4700000000000002</v>
       </c>
-      <c r="F96">
+      <c r="H96" s="1">
         <v>0.11</v>
       </c>
-      <c r="G96">
+      <c r="I96" s="1">
+        <f t="shared" si="5"/>
+        <v>2.9590000000000003E-3</v>
+      </c>
+      <c r="J96">
         <v>2.58</v>
       </c>
-      <c r="H96">
+      <c r="K96">
         <v>5.05</v>
       </c>
-      <c r="I96">
+      <c r="L96">
         <v>4314</v>
       </c>
-      <c r="J96">
+      <c r="M96">
         <v>4316</v>
       </c>
-      <c r="K96">
+      <c r="N96">
         <v>4315</v>
       </c>
-      <c r="L96">
+      <c r="O96">
         <v>62</v>
       </c>
-      <c r="M96">
+      <c r="P96">
         <v>63</v>
       </c>
-      <c r="N96">
+      <c r="Q96">
         <v>63</v>
       </c>
-      <c r="O96">
+      <c r="R96">
         <v>804</v>
       </c>
-      <c r="P96">
+      <c r="S96">
         <v>804</v>
       </c>
-      <c r="Q96">
+      <c r="T96">
         <v>804</v>
       </c>
-      <c r="R96">
+      <c r="U96">
         <v>3447</v>
       </c>
-      <c r="S96">
+      <c r="V96">
         <v>3449</v>
       </c>
-      <c r="T96">
+      <c r="W96">
         <v>3448</v>
       </c>
     </row>
